--- a/data-sources/属性表.xlsx
+++ b/data-sources/属性表.xlsx
@@ -436,7 +436,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="1082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="1086">
   <si>
     <t>属性名</t>
   </si>
@@ -876,39 +876,39 @@
     <t>施法速度比例</t>
   </si>
   <si>
+    <t>missileSpeed</t>
+  </si>
+  <si>
+    <t>投射物速度</t>
+  </si>
+  <si>
+    <t>投射物速度比例</t>
+  </si>
+  <si>
+    <t>attackSpeedRatio</t>
+  </si>
+  <si>
+    <t>作用于调整mainTag=1的技能的attackSpeed字段，attackSpeed=配置值*属性值，默认值为100%</t>
+  </si>
+  <si>
+    <t>castSpeedRatio</t>
+  </si>
+  <si>
+    <t>作用于调整mainTag=2的技能的attackSpeed字段，attackSpeed=配置值*属性值，默认值为100%</t>
+  </si>
+  <si>
+    <t>baseCritRate</t>
+  </si>
+  <si>
+    <t>基础暴击率</t>
+  </si>
+  <si>
+    <t>基础暴击概率百分比</t>
+  </si>
+  <si>
     <t>a.critIsLucky?1-(1-a.baseCritRate)*(1-a.baseCritRate):a.baseCritRate</t>
   </si>
   <si>
-    <t>missileSpeed</t>
-  </si>
-  <si>
-    <t>投射物速度</t>
-  </si>
-  <si>
-    <t>投射物速度比例</t>
-  </si>
-  <si>
-    <t>attackSpeedRatio</t>
-  </si>
-  <si>
-    <t>作用于调整mainTag=1的技能的attackSpeed字段，attackSpeed=配置值*属性值，默认值为100%</t>
-  </si>
-  <si>
-    <t>castSpeedRatio</t>
-  </si>
-  <si>
-    <t>作用于调整mainTag=2的技能的attackSpeed字段，attackSpeed=配置值*属性值，默认值为100%</t>
-  </si>
-  <si>
-    <t>baseCritRate</t>
-  </si>
-  <si>
-    <t>基础暴击率</t>
-  </si>
-  <si>
-    <t>基础暴击概率百分比</t>
-  </si>
-  <si>
     <t>allCritRatePct</t>
   </si>
   <si>
@@ -1987,6 +1987,18 @@
   </si>
   <si>
     <t>强化技能冷却回复效率</t>
+  </si>
+  <si>
+    <t>freezeAilmentReduction</t>
+  </si>
+  <si>
+    <t>冻结异常状态抵抗</t>
+  </si>
+  <si>
+    <t>electrocuteAilmentReduction</t>
+  </si>
+  <si>
+    <t>触电异常状态抵抗</t>
   </si>
   <si>
     <t>玩家当前持有武器类型</t>
@@ -3913,12 +3925,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5135,7 +5147,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AD165"/>
+  <dimension ref="A1:AD167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34.625" customWidth="1"/>
@@ -6288,6 +6300,9 @@
         <v>0</v>
       </c>
       <c r="U17" s="54"/>
+      <c r="Z17" s="32">
+        <v>1</v>
+      </c>
       <c r="AB17" t="s">
         <v>113</v>
       </c>
@@ -6881,19 +6896,16 @@
         <v>0</v>
       </c>
       <c r="U27" s="20"/>
-      <c r="AB27" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="28" s="38" customFormat="1" ht="30" customHeight="1" spans="1:28">
       <c r="A28" s="38" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B28" s="38">
         <v>10033</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D28" s="60" cm="1">
         <f t="array" ref="D28">_xlfn.SWITCH(Q28,1,0,2,2,3,2)</f>
@@ -6904,13 +6916,13 @@
         <v>1</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G28" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="H28" s="38" t="s">
         <v>148</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>149</v>
       </c>
       <c r="I28" s="38" t="s">
         <v>69</v>
@@ -6946,7 +6958,7 @@
     </row>
     <row r="29" customFormat="1" ht="30" customHeight="1" spans="1:28">
       <c r="A29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B29">
         <v>10034</v>
@@ -6963,7 +6975,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G29" t="s">
         <v>141</v>
@@ -7005,7 +7017,7 @@
     </row>
     <row r="30" customFormat="1" ht="30" customHeight="1" spans="1:28">
       <c r="A30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B30">
         <v>10035</v>
@@ -7022,7 +7034,7 @@
         <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G30" t="s">
         <v>145</v>
@@ -7064,13 +7076,13 @@
     </row>
     <row r="31" s="35" customFormat="1" spans="1:28">
       <c r="A31" s="35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B31" s="35">
         <v>10100</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D31" s="52" cm="1">
         <f t="array" ref="D31">_xlfn.SWITCH(Q31,1,0,2,2,3,2)</f>
@@ -7081,13 +7093,13 @@
         <v>2</v>
       </c>
       <c r="F31" s="52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G31" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="H31" s="52" t="s">
         <v>155</v>
-      </c>
-      <c r="H31" s="52" t="s">
-        <v>156</v>
       </c>
       <c r="I31" s="35" t="s">
         <v>69</v>
@@ -7124,6 +7136,12 @@
       </c>
       <c r="V31" s="35">
         <v>1</v>
+      </c>
+      <c r="Z31" s="35">
+        <v>2</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="32" s="35" customFormat="1" spans="1:28">
@@ -15341,78 +15359,208 @@
         <v>0</v>
       </c>
     </row>
+    <row r="166" s="35" customFormat="1" spans="1:22">
+      <c r="A166" s="35" t="s">
+        <v>517</v>
+      </c>
+      <c r="B166">
+        <v>11077</v>
+      </c>
+      <c r="C166" s="35" t="s">
+        <v>518</v>
+      </c>
+      <c r="D166" s="52" cm="1">
+        <f t="array" ref="D166">_xlfn.SWITCH(Q166,1,0,2,2,3,2)</f>
+        <v>2</v>
+      </c>
+      <c r="E166" s="52" cm="1">
+        <f t="array" ref="E166">_xlfn.SWITCH(Q166,1,1,2,2,3,1)</f>
+        <v>2</v>
+      </c>
+      <c r="F166" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="G166" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="H166" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="I166" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="J166" s="35">
+        <v>0</v>
+      </c>
+      <c r="K166" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="L166" s="35">
+        <v>0</v>
+      </c>
+      <c r="M166" s="35">
+        <v>2</v>
+      </c>
+      <c r="N166" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="35">
+        <v>2</v>
+      </c>
+      <c r="R166" s="35">
+        <v>1</v>
+      </c>
+      <c r="S166" s="53">
+        <v>0</v>
+      </c>
+      <c r="T166" s="53">
+        <v>0</v>
+      </c>
+      <c r="U166" s="53"/>
+    </row>
+    <row r="167" s="35" customFormat="1" spans="1:22">
+      <c r="A167" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="B167">
+        <v>11078</v>
+      </c>
+      <c r="C167" s="35" t="s">
+        <v>520</v>
+      </c>
+      <c r="D167" s="52" cm="1">
+        <f t="array" ref="D167">_xlfn.SWITCH(Q167,1,0,2,2,3,2)</f>
+        <v>2</v>
+      </c>
+      <c r="E167" s="52" cm="1">
+        <f t="array" ref="E167">_xlfn.SWITCH(Q167,1,1,2,2,3,1)</f>
+        <v>2</v>
+      </c>
+      <c r="F167" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="G167" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="H167" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="I167" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="J167" s="35">
+        <v>0</v>
+      </c>
+      <c r="K167" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="L167" s="35">
+        <v>0</v>
+      </c>
+      <c r="M167" s="35">
+        <v>2</v>
+      </c>
+      <c r="N167" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="35">
+        <v>2</v>
+      </c>
+      <c r="R167" s="35">
+        <v>1</v>
+      </c>
+      <c r="S167" s="53">
+        <v>0</v>
+      </c>
+      <c r="T167" s="53">
+        <v>0</v>
+      </c>
+      <c r="U167" s="53"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B44">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75">
     <cfRule type="duplicateValues" dxfId="0" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B75">
+  <conditionalFormatting sqref="B76">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B92">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B111">
     <cfRule type="duplicateValues" dxfId="0" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B76">
+  <conditionalFormatting sqref="B134">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B135">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B166">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C166">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B167">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C167">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:B27">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67:B73">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B93:B110">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B112:B115">
     <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  <conditionalFormatting sqref="B116:B119">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
+  <conditionalFormatting sqref="B120:B133">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B134">
+  <conditionalFormatting sqref="B136:B141">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B135">
+  <conditionalFormatting sqref="B152:B156">
     <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26:B27">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  <conditionalFormatting sqref="B162:B164">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B67:B73">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  <conditionalFormatting sqref="C162:C164">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B93:B110">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  <conditionalFormatting sqref="F157:F161">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B112:B115">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B116:B119">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B120:B133">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B136:B141">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B152:B156">
+  <conditionalFormatting sqref="G157:G161">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B162:B164">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C162:C164">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F157:F161">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G157:G161">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H157:H161">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B25 B28:B43 B45 B47:B66 B74 B78:B91 B142:B151">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C161 C165:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="C1:C161 C165 C168:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46 B48 B50 B52 B54 B56 B58 B60">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3">
@@ -15438,18 +15586,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B1" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:2">
       <c r="A2" s="30" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:2">
@@ -15465,7 +15613,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -15473,7 +15621,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15481,7 +15629,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15489,7 +15637,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -15497,7 +15645,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15505,7 +15653,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -15513,7 +15661,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -15521,7 +15669,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -15529,7 +15677,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -15537,7 +15685,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -15545,7 +15693,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -15553,7 +15701,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -15561,7 +15709,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -15588,16 +15736,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D1" s="21" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:6">
@@ -15639,12 +15787,12 @@
         <v>121</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="28" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B5" s="28">
         <v>3002</v>
@@ -15667,7 +15815,7 @@
         <v>101</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15681,12 +15829,12 @@
         <v>102</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="28" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B8" s="28">
         <v>3005</v>
@@ -15695,12 +15843,12 @@
         <v>116</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="28" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B9" s="28">
         <v>3006</v>
@@ -15709,12 +15857,12 @@
         <v>201</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="28" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B10" s="28">
         <v>3007</v>
@@ -15723,12 +15871,12 @@
         <v>202</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="28" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B11" s="28">
         <v>3008</v>
@@ -15737,12 +15885,12 @@
         <v>203</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="28" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B12" s="28">
         <v>3009</v>
@@ -15751,12 +15899,12 @@
         <v>301</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="28" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B13" s="28">
         <v>3010</v>
@@ -15765,12 +15913,12 @@
         <v>302</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="28" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B14" s="28">
         <v>3011</v>
@@ -15779,7 +15927,7 @@
         <v>303</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15812,7 +15960,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="28" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B17" s="28">
         <v>3014</v>
@@ -15821,12 +15969,12 @@
         <v>2002</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="28" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B18" s="28">
         <v>3015</v>
@@ -15840,7 +15988,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="28" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B19" s="28">
         <v>3016</v>
@@ -15849,26 +15997,26 @@
         <v>447</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="29" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B20" s="29">
         <v>3017</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="28" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B21" s="28">
         <v>3018</v>
@@ -15877,7 +16025,7 @@
         <v>115</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -15891,12 +16039,12 @@
         <v>424</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="28" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B23" s="28">
         <v>3020</v>
@@ -15905,12 +16053,12 @@
         <v>448</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="28" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B24" s="28">
         <v>3021</v>
@@ -15919,12 +16067,12 @@
         <v>437</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="28" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B25" s="28">
         <v>3022</v>
@@ -15933,12 +16081,12 @@
         <v>438</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="28" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B26" s="28">
         <v>3023</v>
@@ -15947,12 +16095,12 @@
         <v>439</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="28" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B27" s="28">
         <v>3024</v>
@@ -15961,292 +16109,292 @@
         <v>440</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="29" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B28" s="29">
         <v>3025</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="29" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B29" s="29">
         <v>3026</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="29" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B30" s="29">
         <v>3027</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="29" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B31" s="29">
         <v>3028</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="29" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B32" s="29">
         <v>3029</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="29" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B33" s="29">
         <v>3030</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="29" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B34" s="29">
         <v>3031</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="29" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B35" s="29">
         <v>3032</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="29" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B36" s="29">
         <v>3033</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="29" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B37" s="29">
         <v>3034</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="29" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B38" s="29">
         <v>3035</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="29" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B39" s="29">
         <v>3036</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="29" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B40" s="29">
         <v>3037</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="29" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B41" s="29">
         <v>3038</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="29" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B42" s="29">
         <v>3039</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="29" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B43" s="29">
         <v>3040</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="29" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B44" s="29">
         <v>3041</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="29" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B45" s="29">
         <v>3042</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="29" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B46" s="29">
         <v>3043</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="29" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B47" s="29">
         <v>3044</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="28" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B48" s="28">
         <v>3045</v>
@@ -16255,12 +16403,12 @@
         <v>429</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="28" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B49" s="28">
         <v>3046</v>
@@ -16269,12 +16417,12 @@
         <v>430</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="28" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B50" s="28">
         <v>3047</v>
@@ -16283,12 +16431,12 @@
         <v>431</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="28" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B51" s="28">
         <v>3048</v>
@@ -16297,12 +16445,12 @@
         <v>432</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="28" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B52" s="28">
         <v>3049</v>
@@ -16311,12 +16459,12 @@
         <v>467</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="28" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B53" s="28">
         <v>3050</v>
@@ -16325,12 +16473,12 @@
         <v>468</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="28" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B54" s="28">
         <v>3051</v>
@@ -16339,12 +16487,12 @@
         <v>433</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="28" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B55" s="28">
         <v>3052</v>
@@ -16353,12 +16501,12 @@
         <v>434</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="28" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B56" s="28">
         <v>3053</v>
@@ -16367,12 +16515,12 @@
         <v>435</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="28" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B57" s="28">
         <v>3054</v>
@@ -16381,12 +16529,12 @@
         <v>436</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="28" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B58" s="28">
         <v>3055</v>
@@ -16395,12 +16543,12 @@
         <v>450</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="28" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B59" s="28">
         <v>3056</v>
@@ -16409,40 +16557,40 @@
         <v>451</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="29" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B60" s="29">
         <v>3057</v>
       </c>
       <c r="C60" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="29" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B61" s="29">
         <v>3058</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="28" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B62" s="28">
         <v>3059</v>
@@ -16451,12 +16599,12 @@
         <v>117</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="28" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B63" s="28">
         <v>3060</v>
@@ -16465,12 +16613,12 @@
         <v>118</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="28" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B64" s="28">
         <v>3061</v>
@@ -16479,12 +16627,12 @@
         <v>1007</v>
       </c>
       <c r="D64" s="28" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="28" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B65" s="28">
         <v>3062</v>
@@ -16493,12 +16641,12 @@
         <v>1008</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="28" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B66" s="28">
         <v>3063</v>
@@ -16507,12 +16655,12 @@
         <v>417</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="28" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B67" s="28">
         <v>3064</v>
@@ -16521,12 +16669,12 @@
         <v>418</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="28" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B68" s="28">
         <v>3065</v>
@@ -16535,12 +16683,12 @@
         <v>419</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="28" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B69" s="28">
         <v>3066</v>
@@ -16549,12 +16697,12 @@
         <v>427</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="28" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B70" s="28">
         <v>3067</v>
@@ -16563,12 +16711,12 @@
         <v>428</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="28" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B71" s="28">
         <v>3068</v>
@@ -16577,12 +16725,12 @@
         <v>505</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="28" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B72" s="28">
         <v>3069</v>
@@ -16591,12 +16739,12 @@
         <v>511</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="28" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B73" s="28">
         <v>3070</v>
@@ -16605,12 +16753,12 @@
         <v>513</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="28" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B74" s="28">
         <v>3071</v>
@@ -16619,7 +16767,7 @@
         <v>514</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -16633,12 +16781,12 @@
         <v>515</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="28" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B76" s="28">
         <v>3073</v>
@@ -16647,12 +16795,12 @@
         <v>516</v>
       </c>
       <c r="D76" s="28" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="28" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B77" s="28">
         <v>3074</v>
@@ -16686,7 +16834,7 @@
         <v>3076</v>
       </c>
       <c r="C79" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D79" s="29" t="s">
         <v>262</v>
@@ -16700,7 +16848,7 @@
         <v>3077</v>
       </c>
       <c r="C80" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D80" s="29" t="s">
         <v>265</v>
@@ -16717,7 +16865,7 @@
         <v>110</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -16731,7 +16879,7 @@
         <v>111</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -16764,27 +16912,27 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="6" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>34</v>
@@ -16793,7 +16941,7 @@
         <v>35</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>45</v>
@@ -16827,10 +16975,10 @@
         <v>10031</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -16839,7 +16987,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -16847,10 +16995,10 @@
         <v>10032</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -16859,7 +17007,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -16867,19 +17015,19 @@
         <v>10033</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>679</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -16887,10 +17035,10 @@
         <v>10034</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
@@ -16899,7 +17047,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -16907,10 +17055,10 @@
         <v>10035</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -16919,7 +17067,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -16927,10 +17075,10 @@
         <v>10036</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -16939,7 +17087,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -16947,10 +17095,10 @@
         <v>10037</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -16959,7 +17107,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -16967,10 +17115,10 @@
         <v>10038</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -16979,7 +17127,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -16987,10 +17135,10 @@
         <v>10039</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D12" s="2">
         <v>2</v>
@@ -16999,7 +17147,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -17007,10 +17155,10 @@
         <v>10040</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
@@ -17019,7 +17167,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -17027,10 +17175,10 @@
         <v>10041</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
@@ -17039,7 +17187,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -17047,10 +17195,10 @@
         <v>10042</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
@@ -17059,7 +17207,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -17067,10 +17215,10 @@
         <v>10043</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -17079,7 +17227,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -17087,10 +17235,10 @@
         <v>10044</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -17099,7 +17247,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -17107,10 +17255,10 @@
         <v>10045</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
@@ -17119,7 +17267,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -17127,10 +17275,10 @@
         <v>10046</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
@@ -17139,7 +17287,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -17147,10 +17295,10 @@
         <v>10047</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -17159,7 +17307,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -17167,10 +17315,10 @@
         <v>10048</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
@@ -17179,7 +17327,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -17187,10 +17335,10 @@
         <v>10049</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -17199,7 +17347,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -17207,10 +17355,10 @@
         <v>10050</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="D23" s="2">
         <v>2</v>
@@ -17219,7 +17367,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -17227,10 +17375,10 @@
         <v>10051</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -17239,7 +17387,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -17247,10 +17395,10 @@
         <v>10052</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
@@ -17259,7 +17407,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -17270,7 +17418,7 @@
         <v>445</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
@@ -17279,7 +17427,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -17290,7 +17438,7 @@
         <v>390</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -17299,7 +17447,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -17307,10 +17455,10 @@
         <v>10055</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
@@ -17319,7 +17467,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -17327,10 +17475,10 @@
         <v>10056</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
@@ -17339,7 +17487,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -17347,10 +17495,10 @@
         <v>10057</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D30" s="2">
         <v>2</v>
@@ -17359,7 +17507,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -17367,10 +17515,10 @@
         <v>10058</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="D31" s="2">
         <v>2</v>
@@ -17379,7 +17527,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -17387,10 +17535,10 @@
         <v>10059</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D32" s="2">
         <v>2</v>
@@ -17399,7 +17547,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -17407,10 +17555,10 @@
         <v>10060</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D33" s="2">
         <v>2</v>
@@ -17419,7 +17567,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -17427,10 +17575,10 @@
         <v>10061</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D34" s="2">
         <v>2</v>
@@ -17439,7 +17587,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -17447,10 +17595,10 @@
         <v>10062</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="D35" s="2">
         <v>2</v>
@@ -17459,7 +17607,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -17467,10 +17615,10 @@
         <v>10063</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D36" s="2">
         <v>2</v>
@@ -17479,7 +17627,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -17487,10 +17635,10 @@
         <v>10064</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="D37" s="2">
         <v>2</v>
@@ -17499,7 +17647,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -17507,10 +17655,10 @@
         <v>10065</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="D38" s="2">
         <v>2</v>
@@ -17519,7 +17667,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -17530,7 +17678,7 @@
         <v>178</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D39" s="2">
         <v>2</v>
@@ -17539,7 +17687,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -17550,7 +17698,7 @@
         <v>182</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="D40" s="2">
         <v>2</v>
@@ -17559,7 +17707,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -17567,10 +17715,10 @@
         <v>10068</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D41" s="2">
         <v>2</v>
@@ -17579,7 +17727,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -17587,10 +17735,10 @@
         <v>10069</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D42" s="2">
         <v>2</v>
@@ -17599,7 +17747,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -17607,10 +17755,10 @@
         <v>10070</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D43" s="2">
         <v>2</v>
@@ -17619,7 +17767,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -17627,10 +17775,10 @@
         <v>10071</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="D44" s="2">
         <v>2</v>
@@ -17639,7 +17787,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -17647,10 +17795,10 @@
         <v>10072</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D45" s="2">
         <v>2</v>
@@ -17659,7 +17807,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -17667,10 +17815,10 @@
         <v>10073</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D46" s="2">
         <v>2</v>
@@ -17679,7 +17827,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -17687,10 +17835,10 @@
         <v>10074</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D47" s="2">
         <v>2</v>
@@ -17699,7 +17847,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -17707,10 +17855,10 @@
         <v>10075</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D48" s="2">
         <v>2</v>
@@ -17719,7 +17867,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -17727,10 +17875,10 @@
         <v>10076</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D49" s="2">
         <v>2</v>
@@ -17739,7 +17887,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -17747,10 +17895,10 @@
         <v>10077</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
@@ -17759,7 +17907,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -17767,10 +17915,10 @@
         <v>10078</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="D51" s="2">
         <v>2</v>
@@ -17779,7 +17927,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -17787,10 +17935,10 @@
         <v>10079</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="D52" s="2">
         <v>2</v>
@@ -17799,7 +17947,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -17807,10 +17955,10 @@
         <v>10080</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="D53" s="2">
         <v>2</v>
@@ -17819,7 +17967,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -17827,10 +17975,10 @@
         <v>10081</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D54" s="2">
         <v>2</v>
@@ -17839,7 +17987,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -17847,10 +17995,10 @@
         <v>10082</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="D55" s="2">
         <v>2</v>
@@ -17859,7 +18007,7 @@
         <v>2</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -17867,10 +18015,10 @@
         <v>10083</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D56" s="2">
         <v>2</v>
@@ -17879,7 +18027,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -17887,10 +18035,10 @@
         <v>10084</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D57" s="2">
         <v>2</v>
@@ -17899,7 +18047,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="58" ht="34.5" spans="1:6">
@@ -17907,10 +18055,10 @@
         <v>10085</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="D58" s="2">
         <v>2</v>
@@ -17919,7 +18067,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="59" ht="34.5" spans="1:6">
@@ -17927,10 +18075,10 @@
         <v>10086</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="D59" s="2">
         <v>2</v>
@@ -17939,7 +18087,7 @@
         <v>2</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -17947,10 +18095,10 @@
         <v>10087</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D60" s="2">
         <v>2</v>
@@ -17959,7 +18107,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -17967,10 +18115,10 @@
         <v>10088</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D61" s="2">
         <v>2</v>
@@ -17979,7 +18127,7 @@
         <v>2</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -17987,10 +18135,10 @@
         <v>10089</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D62" s="2">
         <v>2</v>
@@ -17999,7 +18147,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -18007,10 +18155,10 @@
         <v>10090</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="D63" s="2">
         <v>2</v>
@@ -18019,7 +18167,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -18027,10 +18175,10 @@
         <v>10091</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D64" s="2">
         <v>2</v>
@@ -18039,7 +18187,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -18047,10 +18195,10 @@
         <v>10092</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="D65" s="2">
         <v>2</v>
@@ -18059,7 +18207,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -18067,10 +18215,10 @@
         <v>10093</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D66" s="2">
         <v>2</v>
@@ -18079,7 +18227,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -18087,10 +18235,10 @@
         <v>10094</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="D67" s="2">
         <v>2</v>
@@ -18099,7 +18247,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -18107,10 +18255,10 @@
         <v>10095</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D68" s="2">
         <v>2</v>
@@ -18119,7 +18267,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -18127,10 +18275,10 @@
         <v>10096</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D69" s="2">
         <v>2</v>
@@ -18139,7 +18287,7 @@
         <v>2</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -18147,10 +18295,10 @@
         <v>10097</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D70" s="2">
         <v>2</v>
@@ -18159,7 +18307,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -18167,10 +18315,10 @@
         <v>10098</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D71" s="2">
         <v>2</v>
@@ -18179,7 +18327,7 @@
         <v>2</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -18187,10 +18335,10 @@
         <v>10099</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D72" s="2">
         <v>2</v>
@@ -18199,7 +18347,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -18207,10 +18355,10 @@
         <v>10100</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
@@ -18219,7 +18367,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -18227,10 +18375,10 @@
         <v>10101</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="D74" s="2">
         <v>2</v>
@@ -18239,7 +18387,7 @@
         <v>2</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -18247,10 +18395,10 @@
         <v>10102</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D75" s="2">
         <v>2</v>
@@ -18259,7 +18407,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -18267,10 +18415,10 @@
         <v>10103</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="D76" s="2">
         <v>2</v>
@@ -18279,7 +18427,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -18287,10 +18435,10 @@
         <v>10104</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="D77" s="2">
         <v>2</v>
@@ -18299,7 +18447,7 @@
         <v>2</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -18307,10 +18455,10 @@
         <v>10105</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D78" s="2">
         <v>2</v>
@@ -18319,7 +18467,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -18327,10 +18475,10 @@
         <v>10106</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="D79" s="2">
         <v>2</v>
@@ -18339,7 +18487,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -18347,10 +18495,10 @@
         <v>10107</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="D80" s="2">
         <v>2</v>
@@ -18359,7 +18507,7 @@
         <v>2</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -18367,10 +18515,10 @@
         <v>10108</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="D81" s="2">
         <v>2</v>
@@ -18379,7 +18527,7 @@
         <v>2</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -18387,10 +18535,10 @@
         <v>10109</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="D82" s="2">
         <v>2</v>
@@ -18399,7 +18547,7 @@
         <v>2</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -18407,10 +18555,10 @@
         <v>10110</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="D83" s="2">
         <v>2</v>
@@ -18419,7 +18567,7 @@
         <v>2</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -18427,10 +18575,10 @@
         <v>10111</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D84" s="2">
         <v>2</v>
@@ -18439,7 +18587,7 @@
         <v>2</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -18447,10 +18595,10 @@
         <v>10112</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="D85" s="2">
         <v>2</v>
@@ -18459,7 +18607,7 @@
         <v>2</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -18467,10 +18615,10 @@
         <v>10113</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D86" s="2">
         <v>2</v>
@@ -18479,7 +18627,7 @@
         <v>2</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -18487,10 +18635,10 @@
         <v>10114</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D87" s="2">
         <v>2</v>
@@ -18499,7 +18647,7 @@
         <v>2</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -18507,10 +18655,10 @@
         <v>10116</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D88" s="2">
         <v>2</v>
@@ -18519,7 +18667,7 @@
         <v>2</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -18527,10 +18675,10 @@
         <v>10117</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D89" s="2">
         <v>0</v>
@@ -18539,7 +18687,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -18547,10 +18695,10 @@
         <v>10118</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="D90" s="2">
         <v>2</v>
@@ -18559,7 +18707,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -18567,10 +18715,10 @@
         <v>10119</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D91" s="2">
         <v>2</v>
@@ -18579,7 +18727,7 @@
         <v>2</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -18590,7 +18738,7 @@
         <v>195</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="D92" s="2">
         <v>2</v>
@@ -18599,7 +18747,7 @@
         <v>2</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -18607,7 +18755,7 @@
         <v>10121</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="D93" s="2">
         <v>2</v>
@@ -18616,7 +18764,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -18624,10 +18772,10 @@
         <v>10122</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="D94" s="2">
         <v>0</v>
@@ -18636,7 +18784,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -18644,10 +18792,10 @@
         <v>10123</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="D95" s="2">
         <v>2</v>
@@ -18656,7 +18804,7 @@
         <v>2</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -18664,10 +18812,10 @@
         <v>10124</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="D96" s="2">
         <v>2</v>
@@ -18676,7 +18824,7 @@
         <v>2</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -18684,10 +18832,10 @@
         <v>10125</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D97" s="2">
         <v>2</v>
@@ -18696,7 +18844,7 @@
         <v>2</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -18704,10 +18852,10 @@
         <v>10126</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="D98" s="2">
         <v>2</v>
@@ -18716,7 +18864,7 @@
         <v>2</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -18724,10 +18872,10 @@
         <v>10127</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D99" s="2">
         <v>2</v>
@@ -18736,7 +18884,7 @@
         <v>2</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -18744,10 +18892,10 @@
         <v>10128</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D100" s="2">
         <v>2</v>
@@ -18756,7 +18904,7 @@
         <v>2</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -18764,10 +18912,10 @@
         <v>10129</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="D101" s="2">
         <v>0</v>
@@ -18776,7 +18924,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -18784,10 +18932,10 @@
         <v>10130</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D102" s="2">
         <v>2</v>
@@ -18796,7 +18944,7 @@
         <v>2</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -18804,10 +18952,10 @@
         <v>10131</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D103" s="2">
         <v>0</v>
@@ -18816,7 +18964,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -18824,10 +18972,10 @@
         <v>10132</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D104" s="2">
         <v>2</v>
@@ -18836,7 +18984,7 @@
         <v>2</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -18844,10 +18992,10 @@
         <v>10134</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="D105" s="2">
         <v>2</v>
@@ -18856,7 +19004,7 @@
         <v>2</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -18864,10 +19012,10 @@
         <v>10135</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D106" s="2">
         <v>2</v>
@@ -18876,7 +19024,7 @@
         <v>2</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -18884,10 +19032,10 @@
         <v>10136</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="D107" s="2">
         <v>2</v>
@@ -18896,7 +19044,7 @@
         <v>2</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -18904,10 +19052,10 @@
         <v>10137</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="D108" s="2">
         <v>2</v>
@@ -18916,7 +19064,7 @@
         <v>2</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -18924,10 +19072,10 @@
         <v>10138</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D109" s="2">
         <v>2</v>
@@ -18936,7 +19084,7 @@
         <v>2</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -18944,10 +19092,10 @@
         <v>10139</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D110" s="2">
         <v>0</v>
@@ -18956,7 +19104,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -18964,10 +19112,10 @@
         <v>10140</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="D111" s="2">
         <v>2</v>
@@ -18976,7 +19124,7 @@
         <v>2</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -18984,10 +19132,10 @@
         <v>10141</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="D112" s="2">
         <v>0</v>
@@ -18996,7 +19144,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -19004,10 +19152,10 @@
         <v>10142</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D113" s="2">
         <v>2</v>
@@ -19016,7 +19164,7 @@
         <v>2</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -19024,10 +19172,10 @@
         <v>10143</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D114" s="2">
         <v>2</v>
@@ -19036,7 +19184,7 @@
         <v>2</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -19044,10 +19192,10 @@
         <v>10144</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D115" s="2">
         <v>2</v>
@@ -19056,7 +19204,7 @@
         <v>2</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -19064,10 +19212,10 @@
         <v>10145</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D116" s="2">
         <v>0</v>
@@ -19076,7 +19224,7 @@
         <v>0</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -19084,10 +19232,10 @@
         <v>10146</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="D117" s="2">
         <v>2</v>
@@ -19096,7 +19244,7 @@
         <v>2</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -19104,10 +19252,10 @@
         <v>10147</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="D118" s="2">
         <v>2</v>
@@ -19116,7 +19264,7 @@
         <v>2</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -19124,10 +19272,10 @@
         <v>10148</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="D119" s="2">
         <v>0</v>
@@ -19136,7 +19284,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -19144,10 +19292,10 @@
         <v>10149</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="D120" s="2">
         <v>0</v>
@@ -19156,7 +19304,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -19164,10 +19312,10 @@
         <v>10150</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="D121" s="2">
         <v>0</v>
@@ -19176,7 +19324,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -19184,10 +19332,10 @@
         <v>10151</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="D122" s="2">
         <v>0</v>
@@ -19196,7 +19344,7 @@
         <v>0</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -19204,10 +19352,10 @@
         <v>10152</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="D123" s="2">
         <v>0</v>
@@ -19216,7 +19364,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -19224,10 +19372,10 @@
         <v>10153</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="D124" s="2">
         <v>0</v>
@@ -19236,7 +19384,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -19244,10 +19392,10 @@
         <v>10154</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="D125" s="2">
         <v>0</v>
@@ -19256,7 +19404,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -19264,10 +19412,10 @@
         <v>10155</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="D126" s="2">
         <v>0</v>
@@ -19276,7 +19424,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -19284,10 +19432,10 @@
         <v>10156</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="D127" s="2">
         <v>0</v>
@@ -19296,7 +19444,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -19304,10 +19452,10 @@
         <v>10157</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="D128" s="2">
         <v>0</v>
@@ -19316,7 +19464,7 @@
         <v>0</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -19324,10 +19472,10 @@
         <v>10158</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="D129" s="2">
         <v>0</v>
@@ -19336,7 +19484,7 @@
         <v>0</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -19344,10 +19492,10 @@
         <v>10159</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="D130" s="2">
         <v>0</v>
@@ -19356,7 +19504,7 @@
         <v>0</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -19364,10 +19512,10 @@
         <v>10160</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D131" s="2">
         <v>0</v>
@@ -19376,7 +19524,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -19384,10 +19532,10 @@
         <v>10161</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="D132" s="2">
         <v>0</v>
@@ -19396,7 +19544,7 @@
         <v>0</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:6">
@@ -19404,10 +19552,10 @@
         <v>10162</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="D133" s="2">
         <v>0</v>
@@ -19416,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:6">
@@ -19424,10 +19572,10 @@
         <v>10167</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="D134" s="2">
         <v>2</v>
@@ -19436,7 +19584,7 @@
         <v>2</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -19444,10 +19592,10 @@
         <v>10168</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D135" s="2">
         <v>2</v>
@@ -19456,7 +19604,7 @@
         <v>2</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -19464,10 +19612,10 @@
         <v>10169</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="D136" s="2">
         <v>2</v>
@@ -19476,7 +19624,7 @@
         <v>2</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -19484,10 +19632,10 @@
         <v>10170</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="D137" s="2">
         <v>2</v>
@@ -19496,7 +19644,7 @@
         <v>2</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -19504,10 +19652,10 @@
         <v>10171</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="D138" s="2">
         <v>2</v>
@@ -19516,7 +19664,7 @@
         <v>2</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -19524,10 +19672,10 @@
         <v>10172</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="D139" s="2">
         <v>2</v>
@@ -19536,7 +19684,7 @@
         <v>2</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -19544,10 +19692,10 @@
         <v>10173</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="D140" s="2">
         <v>2</v>
@@ -19556,7 +19704,7 @@
         <v>2</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -19564,10 +19712,10 @@
         <v>10174</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="D141" s="2">
         <v>2</v>
@@ -19576,7 +19724,7 @@
         <v>2</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -19584,10 +19732,10 @@
         <v>10175</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D142" s="2">
         <v>2</v>
@@ -19596,7 +19744,7 @@
         <v>2</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -19604,10 +19752,10 @@
         <v>10176</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="D143" s="2">
         <v>2</v>
@@ -19616,7 +19764,7 @@
         <v>2</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -19624,10 +19772,10 @@
         <v>10177</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="D144" s="2">
         <v>2</v>
@@ -19636,7 +19784,7 @@
         <v>2</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" spans="1:6">
@@ -19644,10 +19792,10 @@
         <v>10178</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="D145" s="2">
         <v>2</v>
@@ -19656,7 +19804,7 @@
         <v>2</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="146" s="1" customFormat="1" spans="1:6">
@@ -19664,10 +19812,10 @@
         <v>10179</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="D146" s="2">
         <v>2</v>
@@ -19676,7 +19824,7 @@
         <v>2</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="147" s="1" customFormat="1" spans="1:6">
@@ -19684,10 +19832,10 @@
         <v>10180</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="D147" s="2">
         <v>2</v>
@@ -19696,7 +19844,7 @@
         <v>2</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -19704,7 +19852,7 @@
         <v>10181</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="D148" s="2">
         <v>2</v>
@@ -19718,7 +19866,7 @@
         <v>10182</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="D149" s="2">
         <v>2</v>
@@ -19732,7 +19880,7 @@
         <v>10183</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D150" s="2">
         <v>2</v>
@@ -19746,7 +19894,7 @@
         <v>10184</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="D151" s="2">
         <v>2</v>
@@ -19760,7 +19908,7 @@
         <v>10185</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="D152" s="2">
         <v>2</v>
@@ -19774,7 +19922,7 @@
         <v>10186</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D153" s="2">
         <v>2</v>
@@ -19788,7 +19936,7 @@
         <v>10187</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="D154" s="2">
         <v>2</v>
@@ -19802,7 +19950,7 @@
         <v>10188</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="D155" s="2">
         <v>2</v>
@@ -19816,7 +19964,7 @@
         <v>10189</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="D156" s="2">
         <v>2</v>
@@ -19830,7 +19978,7 @@
         <v>10190</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="D157" s="2">
         <v>2</v>
@@ -19844,7 +19992,7 @@
         <v>10191</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="D158" s="2">
         <v>2</v>
@@ -19858,7 +20006,7 @@
         <v>10192</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="D159" s="2">
         <v>2</v>
@@ -19872,7 +20020,7 @@
         <v>10193</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="D160" s="2">
         <v>2</v>
@@ -19886,7 +20034,7 @@
         <v>10194</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="D161" s="2">
         <v>2</v>
@@ -19900,7 +20048,7 @@
         <v>10195</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="D162" s="2">
         <v>2</v>
@@ -19914,7 +20062,7 @@
         <v>10196</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="D163" s="2">
         <v>2</v>
@@ -19928,7 +20076,7 @@
         <v>10197</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="D164" s="2">
         <v>2</v>
@@ -19942,7 +20090,7 @@
         <v>10198</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="D165" s="2">
         <v>2</v>
@@ -19956,7 +20104,7 @@
         <v>10199</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="D166" s="2">
         <v>2</v>
@@ -19970,7 +20118,7 @@
         <v>10200</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="D167" s="2">
         <v>2</v>
@@ -19984,7 +20132,7 @@
         <v>10201</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="D168" s="2">
         <v>2</v>
@@ -19998,7 +20146,7 @@
         <v>10202</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="D169" s="2">
         <v>2</v>
@@ -20012,7 +20160,7 @@
         <v>10203</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="D170" s="2">
         <v>2</v>
@@ -20026,7 +20174,7 @@
         <v>10204</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="D171" s="2">
         <v>2</v>
@@ -20040,7 +20188,7 @@
         <v>10205</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="D172" s="2">
         <v>2</v>
@@ -20054,7 +20202,7 @@
         <v>10206</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="D173" s="2">
         <v>0</v>
@@ -20068,7 +20216,7 @@
         <v>10207</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="D174" s="2">
         <v>2</v>
@@ -20082,7 +20230,7 @@
         <v>10208</v>
       </c>
       <c r="B175" s="17" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="D175" s="2">
         <v>2</v>
@@ -20096,7 +20244,7 @@
         <v>10209</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="D176" s="2">
         <v>2</v>
@@ -20110,7 +20258,7 @@
         <v>10210</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="D177" s="2">
         <v>2</v>
@@ -20124,7 +20272,7 @@
         <v>10211</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="D178" s="2">
         <v>2</v>
@@ -20138,7 +20286,7 @@
         <v>10212</v>
       </c>
       <c r="B179" s="17" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="D179" s="2">
         <v>2</v>
@@ -20152,7 +20300,7 @@
         <v>10213</v>
       </c>
       <c r="B180" s="17" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="D180" s="2">
         <v>2</v>
@@ -20166,7 +20314,7 @@
         <v>10214</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="D181" s="2">
         <v>2</v>
@@ -20180,7 +20328,7 @@
         <v>10215</v>
       </c>
       <c r="B182" s="17" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="D182" s="2">
         <v>2</v>
@@ -20194,7 +20342,7 @@
         <v>10216</v>
       </c>
       <c r="B183" s="17" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="D183" s="2">
         <v>2</v>
@@ -20208,7 +20356,7 @@
         <v>10217</v>
       </c>
       <c r="B184" s="17" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="D184" s="2">
         <v>2</v>
@@ -20222,7 +20370,7 @@
         <v>10218</v>
       </c>
       <c r="B185" s="17" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="D185" s="2">
         <v>2</v>
@@ -20236,7 +20384,7 @@
         <v>10219</v>
       </c>
       <c r="B186" s="17" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="D186" s="2">
         <v>2</v>
@@ -20250,7 +20398,7 @@
         <v>10220</v>
       </c>
       <c r="B187" s="17" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="D187" s="2">
         <v>2</v>
@@ -20264,7 +20412,7 @@
         <v>10221</v>
       </c>
       <c r="B188" s="17" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D188" s="2">
         <v>2</v>
@@ -20278,7 +20426,7 @@
         <v>10222</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="D189" s="2">
         <v>2</v>
@@ -20292,7 +20440,7 @@
         <v>10223</v>
       </c>
       <c r="B190" s="17" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="D190" s="2">
         <v>2</v>
@@ -20306,7 +20454,7 @@
         <v>10224</v>
       </c>
       <c r="B191" s="17" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="D191" s="2">
         <v>2</v>
@@ -20320,10 +20468,10 @@
         <v>10225</v>
       </c>
       <c r="B192" s="17" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="D192" s="2">
         <v>2</v>
@@ -20337,10 +20485,10 @@
         <v>10226</v>
       </c>
       <c r="B193" s="17" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D193" s="2">
         <v>2</v>
@@ -20354,7 +20502,7 @@
         <v>10227</v>
       </c>
       <c r="B194" s="17" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="D194" s="2">
         <v>2</v>
@@ -20368,7 +20516,7 @@
         <v>10228</v>
       </c>
       <c r="B195" s="17" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="D195" s="2">
         <v>2</v>
@@ -20382,7 +20530,7 @@
         <v>10229</v>
       </c>
       <c r="B196" s="17" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="D196" s="2">
         <v>2</v>
@@ -20396,7 +20544,7 @@
         <v>10230</v>
       </c>
       <c r="B197" s="17" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="D197" s="2">
         <v>2</v>
@@ -20424,7 +20572,7 @@
         <v>10232</v>
       </c>
       <c r="B199" s="17" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="D199" s="2">
         <v>2</v>
@@ -20438,7 +20586,7 @@
         <v>10233</v>
       </c>
       <c r="B200" s="17" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="D200" s="2">
         <v>2</v>
@@ -20452,7 +20600,7 @@
         <v>10234</v>
       </c>
       <c r="B201" s="17" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D201" s="2">
         <v>2</v>
@@ -20466,7 +20614,7 @@
         <v>10235</v>
       </c>
       <c r="B202" s="17" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="D202" s="2">
         <v>2</v>
@@ -20480,7 +20628,7 @@
         <v>10236</v>
       </c>
       <c r="B203" s="17" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="D203" s="2">
         <v>2</v>
@@ -20494,10 +20642,10 @@
         <v>10237</v>
       </c>
       <c r="B204" s="17" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="D204" s="2">
         <v>2</v>
@@ -20511,7 +20659,7 @@
         <v>10238</v>
       </c>
       <c r="B205" s="17" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="D205" s="2">
         <v>2</v>
@@ -20525,7 +20673,7 @@
         <v>10239</v>
       </c>
       <c r="B206" s="17" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="D206" s="2">
         <v>2</v>
@@ -20539,7 +20687,7 @@
         <v>10240</v>
       </c>
       <c r="B207" s="17" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="D207" s="2">
         <v>0</v>
@@ -20553,7 +20701,7 @@
         <v>10241</v>
       </c>
       <c r="B208" s="17" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="D208" s="2">
         <v>0</v>
@@ -20567,7 +20715,7 @@
         <v>10242</v>
       </c>
       <c r="B209" s="17" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D209" s="2">
         <v>0</v>
@@ -20581,10 +20729,10 @@
         <v>10243</v>
       </c>
       <c r="B210" s="17" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="D210" s="2">
         <v>2</v>
@@ -20621,24 +20769,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>34</v>
@@ -20647,7 +20795,7 @@
         <v>35</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>45</v>
@@ -20675,10 +20823,10 @@
         <v>2110000010</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="D4" s="4">
         <v>0</v>
@@ -20692,10 +20840,10 @@
         <v>2110000011</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="D5" s="4">
         <v>0</v>
@@ -20709,10 +20857,10 @@
         <v>2110000012</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="D6" s="4">
         <v>0</v>
@@ -20726,10 +20874,10 @@
         <v>2110000020</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -20743,10 +20891,10 @@
         <v>2110000021</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -20760,10 +20908,10 @@
         <v>2110000030</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="D9" s="4">
         <v>0</v>
@@ -20777,10 +20925,10 @@
         <v>2110000031</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="D10" s="4">
         <v>0</v>
@@ -20794,10 +20942,10 @@
         <v>2110000040</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
@@ -20811,10 +20959,10 @@
         <v>2114000020</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
@@ -20828,10 +20976,10 @@
         <v>2120000010</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -20845,10 +20993,10 @@
         <v>2120000011</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
@@ -20862,10 +21010,10 @@
         <v>2120000020</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="D15" s="4">
         <v>0</v>
@@ -20879,10 +21027,10 @@
         <v>2120000030</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="D16" s="4">
         <v>0</v>
@@ -20896,10 +21044,10 @@
         <v>2120000040</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="D17" s="4">
         <v>0</v>
@@ -20913,10 +21061,10 @@
         <v>2120000060</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -20930,10 +21078,10 @@
         <v>2120000080</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="D19" s="4">
         <v>0</v>
@@ -20947,10 +21095,10 @@
         <v>2140000030</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="D20" s="4">
         <v>0</v>
@@ -20964,10 +21112,10 @@
         <v>2140000040</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
@@ -20981,10 +21129,10 @@
         <v>2140000050</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
@@ -20998,10 +21146,10 @@
         <v>2140000060</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="D23" s="4">
         <v>0</v>
@@ -21015,10 +21163,10 @@
         <v>2140000070</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D24" s="4">
         <v>0</v>
@@ -21032,10 +21180,10 @@
         <v>2140000080</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="D25" s="4">
         <v>0</v>
@@ -21049,10 +21197,10 @@
         <v>2140000110</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D26" s="4">
         <v>0</v>
@@ -21066,10 +21214,10 @@
         <v>2140000140</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -21083,10 +21231,10 @@
         <v>2140000150</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="D28" s="4">
         <v>0</v>
@@ -21100,10 +21248,10 @@
         <v>2140000160</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="D29" s="4">
         <v>0</v>
@@ -21117,10 +21265,10 @@
         <v>2140000170</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="D30" s="4">
         <v>0</v>
@@ -21134,10 +21282,10 @@
         <v>2140000180</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="D31" s="4">
         <v>0</v>
@@ -21151,10 +21299,10 @@
         <v>2150000010</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="D32" s="4">
         <v>0</v>
@@ -21168,10 +21316,10 @@
         <v>2150000020</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -21185,10 +21333,10 @@
         <v>2150000060</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D34" s="4">
         <v>0</v>
@@ -21202,10 +21350,10 @@
         <v>2150000070</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="D35" s="4">
         <v>0</v>
@@ -21219,10 +21367,10 @@
         <v>2150000080</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="D36" s="4">
         <v>0</v>
@@ -21236,10 +21384,10 @@
         <v>2150000090</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D37" s="4">
         <v>0</v>
@@ -21253,10 +21401,10 @@
         <v>2150000091</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
@@ -21270,10 +21418,10 @@
         <v>2150000100</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="D39" s="4">
         <v>0</v>
@@ -21287,10 +21435,10 @@
         <v>2150000110</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="D40" s="4">
         <v>0</v>
@@ -21304,10 +21452,10 @@
         <v>2150100060</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D41" s="4">
         <v>0</v>
@@ -21321,10 +21469,10 @@
         <v>2150100070</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="D42" s="4">
         <v>0</v>
@@ -21338,10 +21486,10 @@
         <v>2150100080</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
@@ -21355,10 +21503,10 @@
         <v>2150100090</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D44" s="4">
         <v>0</v>
@@ -21372,10 +21520,10 @@
         <v>2150100091</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D45" s="4">
         <v>0</v>
@@ -21389,10 +21537,10 @@
         <v>2150200060</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D46" s="4">
         <v>0</v>
@@ -21406,10 +21554,10 @@
         <v>2150200070</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="D47" s="4">
         <v>0</v>
@@ -21423,10 +21571,10 @@
         <v>2150200080</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
@@ -21440,10 +21588,10 @@
         <v>2150200090</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D49" s="4">
         <v>0</v>
@@ -21457,10 +21605,10 @@
         <v>2150200091</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D50" s="4">
         <v>0</v>
@@ -21474,10 +21622,10 @@
         <v>2150300060</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D51" s="4">
         <v>0</v>
@@ -21491,10 +21639,10 @@
         <v>2150300070</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="D52" s="4">
         <v>0</v>
@@ -21508,10 +21656,10 @@
         <v>2150300090</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
@@ -21525,10 +21673,10 @@
         <v>2150300091</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D54" s="4">
         <v>0</v>
@@ -21542,10 +21690,10 @@
         <v>2150400060</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D55" s="4">
         <v>0</v>
@@ -21559,10 +21707,10 @@
         <v>2150400090</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D56" s="4">
         <v>0</v>
@@ -21576,10 +21724,10 @@
         <v>2150400091</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D57" s="4">
         <v>0</v>
@@ -21593,10 +21741,10 @@
         <v>2340000010</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
@@ -21610,10 +21758,10 @@
         <v>2340000020</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="D59" s="4">
         <v>2</v>
@@ -21627,10 +21775,10 @@
         <v>2340000030</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="D60" s="4">
         <v>2</v>
@@ -21644,10 +21792,10 @@
         <v>2340000040</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
@@ -21661,10 +21809,10 @@
         <v>2340000050</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="D62" s="4">
         <v>0</v>
@@ -21678,10 +21826,10 @@
         <v>2340000080</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="D63" s="2">
         <v>0</v>
@@ -21695,10 +21843,10 @@
         <v>3140000020</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="D64" s="4">
         <v>0</v>
@@ -21712,10 +21860,10 @@
         <v>3140000030</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="D65" s="4">
         <v>0</v>
@@ -21729,10 +21877,10 @@
         <v>3140000040</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="D66" s="4">
         <v>0</v>
@@ -21746,10 +21894,10 @@
         <v>2140000100</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>

--- a/data-sources/属性表.xlsx
+++ b/data-sources/属性表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\策划\1.表格目录\XLS表格\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\古荒遗迹2策划\1.表格目录\XLS表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27825" windowHeight="12240"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="AttributeName" sheetId="1" r:id="rId1"/>
@@ -460,7 +460,7 @@
     <t>属性描述</t>
   </si>
   <si>
-    <t>(nouse)词缀描述</t>
+    <t>词缀描述</t>
   </si>
   <si>
     <t>图标</t>

--- a/data-sources/属性表.xlsx
+++ b/data-sources/属性表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\古荒遗迹2策划\1.表格目录\XLS表格\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\zaomeng\1.表格目录\XLS表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="AttributeName" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="StuntDes" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AttributeName!$S$1:$S$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AttributeName!$S$1:$S$181</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -437,7 +437,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="1460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="1463">
   <si>
     <t>属性名</t>
   </si>
@@ -1798,7 +1798,7 @@
     <t>穿戴等级降低</t>
   </si>
   <si>
-    <t>穿戴等级降低增加{0}</t>
+    <t>穿戴等级降低{0}</t>
   </si>
   <si>
     <t>immunityIgniteChance</t>
@@ -2656,9 +2656,6 @@
     <t>强化技能冷却回复效率</t>
   </si>
   <si>
-    <t>强化冷却效率</t>
-  </si>
-  <si>
     <t>强化冷却效率增加{0}</t>
   </si>
   <si>
@@ -2804,6 +2801,18 @@
   </si>
   <si>
     <t>生命魔力回复共用</t>
+  </si>
+  <si>
+    <t>drugRecoveryHP</t>
+  </si>
+  <si>
+    <t>药剂回复生命效果</t>
+  </si>
+  <si>
+    <t>drugRecoveryMP</t>
+  </si>
+  <si>
+    <t>药剂回复魔力效果</t>
   </si>
   <si>
     <t>玩家当前持有武器类型</t>
@@ -6276,7 +6285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AE180"/>
+  <dimension ref="A1:AE182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34.625" customWidth="1"/>
@@ -16935,17 +16944,17 @@
       <c r="E165" s="34">
         <v>2</v>
       </c>
-      <c r="F165" s="34" t="s">
-        <v>699</v>
+      <c r="F165" t="s">
+        <v>738</v>
       </c>
       <c r="G165" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H165" t="s">
         <v>738</v>
       </c>
       <c r="I165" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="J165" t="s">
         <v>73</v>
@@ -16983,13 +16992,13 @@
     </row>
     <row r="166" s="37" customFormat="1" spans="1:31">
       <c r="A166" s="37" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B166">
         <v>11077</v>
       </c>
       <c r="C166" s="37" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D166" s="54" cm="1">
         <f t="array" ref="D166">_xlfn.SWITCH(R166,1,0,2,2,3,2)</f>
@@ -17045,13 +17054,13 @@
     </row>
     <row r="167" s="37" customFormat="1" spans="1:31">
       <c r="A167" s="37" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B167">
         <v>11078</v>
       </c>
       <c r="C167" s="37" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D167" s="54" cm="1">
         <f t="array" ref="D167">_xlfn.SWITCH(R167,1,0,2,2,3,2)</f>
@@ -17107,31 +17116,31 @@
     </row>
     <row r="168" customFormat="1" spans="1:31">
       <c r="A168" s="37" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B168">
         <v>11079</v>
       </c>
       <c r="C168" t="s">
+        <v>745</v>
+      </c>
+      <c r="D168" s="34">
+        <v>2</v>
+      </c>
+      <c r="E168" s="34">
+        <v>2</v>
+      </c>
+      <c r="F168" t="s">
+        <v>745</v>
+      </c>
+      <c r="G168" t="s">
         <v>746</v>
       </c>
-      <c r="D168" s="34">
-        <v>2</v>
-      </c>
-      <c r="E168" s="34">
-        <v>2</v>
-      </c>
-      <c r="F168" t="s">
-        <v>746</v>
-      </c>
-      <c r="G168" t="s">
+      <c r="H168" t="s">
+        <v>745</v>
+      </c>
+      <c r="I168" t="s">
         <v>747</v>
-      </c>
-      <c r="H168" t="s">
-        <v>746</v>
-      </c>
-      <c r="I168" t="s">
-        <v>748</v>
       </c>
       <c r="J168" s="68" t="s">
         <v>73</v>
@@ -17172,31 +17181,31 @@
     </row>
     <row r="169" spans="1:31">
       <c r="A169" s="37" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B169">
         <v>11080</v>
       </c>
       <c r="C169" t="s">
+        <v>749</v>
+      </c>
+      <c r="D169" s="34">
+        <v>2</v>
+      </c>
+      <c r="E169" s="34">
+        <v>2</v>
+      </c>
+      <c r="F169" t="s">
+        <v>749</v>
+      </c>
+      <c r="G169" t="s">
+        <v>749</v>
+      </c>
+      <c r="H169" t="s">
+        <v>749</v>
+      </c>
+      <c r="I169" t="s">
         <v>750</v>
-      </c>
-      <c r="D169" s="34">
-        <v>2</v>
-      </c>
-      <c r="E169" s="34">
-        <v>2</v>
-      </c>
-      <c r="F169" t="s">
-        <v>750</v>
-      </c>
-      <c r="G169" t="s">
-        <v>750</v>
-      </c>
-      <c r="H169" t="s">
-        <v>750</v>
-      </c>
-      <c r="I169" t="s">
-        <v>751</v>
       </c>
       <c r="J169" s="68" t="s">
         <v>73</v>
@@ -17237,31 +17246,31 @@
     </row>
     <row r="170" spans="1:31">
       <c r="A170" s="37" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B170">
         <v>11081</v>
       </c>
       <c r="C170" t="s">
+        <v>752</v>
+      </c>
+      <c r="D170" s="34">
+        <v>2</v>
+      </c>
+      <c r="E170" s="34">
+        <v>2</v>
+      </c>
+      <c r="F170" t="s">
+        <v>752</v>
+      </c>
+      <c r="G170" t="s">
+        <v>752</v>
+      </c>
+      <c r="H170" t="s">
+        <v>752</v>
+      </c>
+      <c r="I170" t="s">
         <v>753</v>
-      </c>
-      <c r="D170" s="34">
-        <v>2</v>
-      </c>
-      <c r="E170" s="34">
-        <v>2</v>
-      </c>
-      <c r="F170" t="s">
-        <v>753</v>
-      </c>
-      <c r="G170" t="s">
-        <v>753</v>
-      </c>
-      <c r="H170" t="s">
-        <v>753</v>
-      </c>
-      <c r="I170" t="s">
-        <v>754</v>
       </c>
       <c r="J170" s="68" t="s">
         <v>73</v>
@@ -17300,31 +17309,31 @@
     </row>
     <row r="171" spans="1:31">
       <c r="A171" s="37" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B171">
         <v>11082</v>
       </c>
       <c r="C171" t="s">
+        <v>755</v>
+      </c>
+      <c r="D171" s="34">
+        <v>2</v>
+      </c>
+      <c r="E171" s="34">
+        <v>2</v>
+      </c>
+      <c r="F171" t="s">
+        <v>755</v>
+      </c>
+      <c r="G171" t="s">
+        <v>755</v>
+      </c>
+      <c r="H171" t="s">
+        <v>755</v>
+      </c>
+      <c r="I171" t="s">
         <v>756</v>
-      </c>
-      <c r="D171" s="34">
-        <v>2</v>
-      </c>
-      <c r="E171" s="34">
-        <v>2</v>
-      </c>
-      <c r="F171" t="s">
-        <v>756</v>
-      </c>
-      <c r="G171" t="s">
-        <v>756</v>
-      </c>
-      <c r="H171" t="s">
-        <v>756</v>
-      </c>
-      <c r="I171" t="s">
-        <v>757</v>
       </c>
       <c r="J171" s="68" t="s">
         <v>73</v>
@@ -17363,31 +17372,31 @@
     </row>
     <row r="172" spans="1:31">
       <c r="A172" s="37" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B172">
         <v>11083</v>
       </c>
       <c r="C172" t="s">
+        <v>758</v>
+      </c>
+      <c r="D172" s="34">
+        <v>2</v>
+      </c>
+      <c r="E172" s="34">
+        <v>2</v>
+      </c>
+      <c r="F172" t="s">
+        <v>758</v>
+      </c>
+      <c r="G172" t="s">
+        <v>758</v>
+      </c>
+      <c r="H172" t="s">
+        <v>758</v>
+      </c>
+      <c r="I172" t="s">
         <v>759</v>
-      </c>
-      <c r="D172" s="34">
-        <v>2</v>
-      </c>
-      <c r="E172" s="34">
-        <v>2</v>
-      </c>
-      <c r="F172" t="s">
-        <v>759</v>
-      </c>
-      <c r="G172" t="s">
-        <v>759</v>
-      </c>
-      <c r="H172" t="s">
-        <v>759</v>
-      </c>
-      <c r="I172" t="s">
-        <v>760</v>
       </c>
       <c r="J172" s="68" t="s">
         <v>73</v>
@@ -17426,31 +17435,31 @@
     </row>
     <row r="173" spans="1:31">
       <c r="A173" s="37" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B173">
         <v>11084</v>
       </c>
       <c r="C173" t="s">
+        <v>761</v>
+      </c>
+      <c r="D173" s="34">
+        <v>2</v>
+      </c>
+      <c r="E173" s="34">
+        <v>2</v>
+      </c>
+      <c r="F173" t="s">
+        <v>761</v>
+      </c>
+      <c r="G173" t="s">
+        <v>761</v>
+      </c>
+      <c r="H173" t="s">
+        <v>761</v>
+      </c>
+      <c r="I173" t="s">
         <v>762</v>
-      </c>
-      <c r="D173" s="34">
-        <v>2</v>
-      </c>
-      <c r="E173" s="34">
-        <v>2</v>
-      </c>
-      <c r="F173" t="s">
-        <v>762</v>
-      </c>
-      <c r="G173" t="s">
-        <v>762</v>
-      </c>
-      <c r="H173" t="s">
-        <v>762</v>
-      </c>
-      <c r="I173" t="s">
-        <v>763</v>
       </c>
       <c r="J173" s="68" t="s">
         <v>73</v>
@@ -17489,31 +17498,31 @@
     </row>
     <row r="174" spans="1:31">
       <c r="A174" s="37" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B174">
         <v>11085</v>
       </c>
       <c r="C174" t="s">
+        <v>764</v>
+      </c>
+      <c r="D174" s="34">
+        <v>2</v>
+      </c>
+      <c r="E174" s="34">
+        <v>2</v>
+      </c>
+      <c r="F174" t="s">
+        <v>764</v>
+      </c>
+      <c r="G174" t="s">
+        <v>764</v>
+      </c>
+      <c r="H174" t="s">
+        <v>764</v>
+      </c>
+      <c r="I174" t="s">
         <v>765</v>
-      </c>
-      <c r="D174" s="34">
-        <v>2</v>
-      </c>
-      <c r="E174" s="34">
-        <v>2</v>
-      </c>
-      <c r="F174" t="s">
-        <v>765</v>
-      </c>
-      <c r="G174" t="s">
-        <v>765</v>
-      </c>
-      <c r="H174" t="s">
-        <v>765</v>
-      </c>
-      <c r="I174" t="s">
-        <v>766</v>
       </c>
       <c r="J174" s="68" t="s">
         <v>73</v>
@@ -17552,31 +17561,31 @@
     </row>
     <row r="175" customFormat="1" spans="1:31">
       <c r="A175" s="37" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B175">
         <v>11086</v>
       </c>
       <c r="C175" t="s">
+        <v>767</v>
+      </c>
+      <c r="D175" s="34">
+        <v>2</v>
+      </c>
+      <c r="E175" s="34">
+        <v>2</v>
+      </c>
+      <c r="F175" t="s">
+        <v>767</v>
+      </c>
+      <c r="G175" t="s">
         <v>768</v>
       </c>
-      <c r="D175" s="34">
-        <v>2</v>
-      </c>
-      <c r="E175" s="34">
-        <v>2</v>
-      </c>
-      <c r="F175" t="s">
-        <v>768</v>
-      </c>
-      <c r="G175" t="s">
+      <c r="H175" t="s">
+        <v>767</v>
+      </c>
+      <c r="I175" t="s">
         <v>769</v>
-      </c>
-      <c r="H175" t="s">
-        <v>768</v>
-      </c>
-      <c r="I175" t="s">
-        <v>770</v>
       </c>
       <c r="J175" s="68" t="s">
         <v>73</v>
@@ -17615,7 +17624,7 @@
       </c>
       <c r="W175" s="68"/>
       <c r="AD175" s="37" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AE175">
         <v>3</v>
@@ -17623,31 +17632,31 @@
     </row>
     <row r="176" customFormat="1" spans="1:31">
       <c r="A176" s="37" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B176">
         <v>11087</v>
       </c>
       <c r="C176" t="s">
+        <v>771</v>
+      </c>
+      <c r="D176" s="34">
+        <v>2</v>
+      </c>
+      <c r="E176" s="34">
+        <v>2</v>
+      </c>
+      <c r="F176" t="s">
+        <v>771</v>
+      </c>
+      <c r="G176" t="s">
         <v>772</v>
       </c>
-      <c r="D176" s="34">
-        <v>2</v>
-      </c>
-      <c r="E176" s="34">
-        <v>2</v>
-      </c>
-      <c r="F176" t="s">
-        <v>772</v>
-      </c>
-      <c r="G176" t="s">
+      <c r="H176" t="s">
+        <v>771</v>
+      </c>
+      <c r="I176" t="s">
         <v>773</v>
-      </c>
-      <c r="H176" t="s">
-        <v>772</v>
-      </c>
-      <c r="I176" t="s">
-        <v>774</v>
       </c>
       <c r="J176" s="68" t="s">
         <v>73</v>
@@ -17686,7 +17695,7 @@
       </c>
       <c r="W176" s="68"/>
       <c r="AD176" s="37" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AE176">
         <v>3</v>
@@ -17694,31 +17703,31 @@
     </row>
     <row r="177" customFormat="1" spans="1:31">
       <c r="A177" s="37" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B177">
         <v>11088</v>
       </c>
       <c r="C177" t="s">
+        <v>775</v>
+      </c>
+      <c r="D177" s="34">
+        <v>2</v>
+      </c>
+      <c r="E177" s="34">
+        <v>2</v>
+      </c>
+      <c r="F177" t="s">
+        <v>775</v>
+      </c>
+      <c r="G177" t="s">
         <v>776</v>
       </c>
-      <c r="D177" s="34">
-        <v>2</v>
-      </c>
-      <c r="E177" s="34">
-        <v>2</v>
-      </c>
-      <c r="F177" t="s">
-        <v>776</v>
-      </c>
-      <c r="G177" t="s">
+      <c r="H177" t="s">
+        <v>775</v>
+      </c>
+      <c r="I177" t="s">
         <v>777</v>
-      </c>
-      <c r="H177" t="s">
-        <v>776</v>
-      </c>
-      <c r="I177" t="s">
-        <v>778</v>
       </c>
       <c r="J177" s="68" t="s">
         <v>73</v>
@@ -17757,7 +17766,7 @@
       </c>
       <c r="W177" s="68"/>
       <c r="AD177" s="37" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AE177">
         <v>3</v>
@@ -17765,31 +17774,31 @@
     </row>
     <row r="178" customFormat="1" spans="1:31">
       <c r="A178" s="37" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B178">
         <v>11089</v>
       </c>
       <c r="C178" t="s">
+        <v>779</v>
+      </c>
+      <c r="D178" s="34">
+        <v>2</v>
+      </c>
+      <c r="E178" s="34">
+        <v>2</v>
+      </c>
+      <c r="F178" t="s">
+        <v>779</v>
+      </c>
+      <c r="G178" t="s">
         <v>780</v>
       </c>
-      <c r="D178" s="34">
-        <v>2</v>
-      </c>
-      <c r="E178" s="34">
-        <v>2</v>
-      </c>
-      <c r="F178" t="s">
-        <v>780</v>
-      </c>
-      <c r="G178" t="s">
+      <c r="H178" t="s">
+        <v>779</v>
+      </c>
+      <c r="I178" t="s">
         <v>781</v>
-      </c>
-      <c r="H178" t="s">
-        <v>780</v>
-      </c>
-      <c r="I178" t="s">
-        <v>782</v>
       </c>
       <c r="J178" s="68" t="s">
         <v>73</v>
@@ -17828,7 +17837,7 @@
       </c>
       <c r="W178" s="68"/>
       <c r="AD178" s="37" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AE178">
         <v>3</v>
@@ -17836,31 +17845,31 @@
     </row>
     <row r="179" customFormat="1" spans="1:31">
       <c r="A179" s="37" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B179">
         <v>11090</v>
       </c>
       <c r="C179" t="s">
+        <v>783</v>
+      </c>
+      <c r="D179" s="34">
+        <v>2</v>
+      </c>
+      <c r="E179" s="34">
+        <v>2</v>
+      </c>
+      <c r="F179" t="s">
+        <v>783</v>
+      </c>
+      <c r="G179" t="s">
         <v>784</v>
       </c>
-      <c r="D179" s="34">
-        <v>2</v>
-      </c>
-      <c r="E179" s="34">
-        <v>2</v>
-      </c>
-      <c r="F179" t="s">
-        <v>784</v>
-      </c>
-      <c r="G179" t="s">
+      <c r="H179" t="s">
+        <v>783</v>
+      </c>
+      <c r="I179" t="s">
         <v>785</v>
-      </c>
-      <c r="H179" t="s">
-        <v>784</v>
-      </c>
-      <c r="I179" t="s">
-        <v>786</v>
       </c>
       <c r="J179" s="68" t="s">
         <v>73</v>
@@ -17899,7 +17908,7 @@
       </c>
       <c r="W179" s="68"/>
       <c r="AD179" s="37" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AE179">
         <v>3</v>
@@ -17907,13 +17916,13 @@
     </row>
     <row r="180" s="43" customFormat="1" ht="16" customHeight="1" spans="1:31">
       <c r="A180" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B180">
         <v>11091</v>
       </c>
       <c r="C180" s="43" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D180" s="70">
         <v>2</v>
@@ -17922,16 +17931,16 @@
         <v>2</v>
       </c>
       <c r="F180" s="43" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G180" s="43" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H180" s="43" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="I180" s="43" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="J180" s="68" t="s">
         <v>73</v>
@@ -17977,177 +17986,345 @@
       <c r="AC180" s="68"/>
       <c r="AD180" s="68"/>
     </row>
+    <row r="181" s="43" customFormat="1" ht="16" customHeight="1" spans="1:31">
+      <c r="A181" t="s">
+        <v>788</v>
+      </c>
+      <c r="B181">
+        <v>11092</v>
+      </c>
+      <c r="C181" s="43" t="s">
+        <v>789</v>
+      </c>
+      <c r="D181" s="70">
+        <v>2</v>
+      </c>
+      <c r="E181" s="71">
+        <v>2</v>
+      </c>
+      <c r="F181" s="43" t="s">
+        <v>789</v>
+      </c>
+      <c r="G181" s="43" t="s">
+        <v>789</v>
+      </c>
+      <c r="H181" s="43" t="s">
+        <v>789</v>
+      </c>
+      <c r="I181" s="43" t="s">
+        <v>789</v>
+      </c>
+      <c r="J181" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="K181" s="68">
+        <v>0</v>
+      </c>
+      <c r="L181" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="M181" s="68">
+        <v>0</v>
+      </c>
+      <c r="N181" s="68">
+        <v>2</v>
+      </c>
+      <c r="O181" s="68">
+        <v>0</v>
+      </c>
+      <c r="P181" s="68"/>
+      <c r="Q181" s="68"/>
+      <c r="R181" s="68">
+        <v>2</v>
+      </c>
+      <c r="S181" s="41">
+        <v>0</v>
+      </c>
+      <c r="T181" s="72">
+        <v>1</v>
+      </c>
+      <c r="U181" s="72">
+        <v>0</v>
+      </c>
+      <c r="V181" s="72">
+        <v>0</v>
+      </c>
+      <c r="W181" s="68"/>
+      <c r="X181" s="68"/>
+      <c r="Y181" s="68"/>
+      <c r="Z181" s="68"/>
+      <c r="AA181" s="68"/>
+      <c r="AB181" s="68"/>
+      <c r="AC181" s="68"/>
+      <c r="AD181" s="68"/>
+    </row>
+    <row r="182" s="43" customFormat="1" ht="16" customHeight="1" spans="1:31">
+      <c r="A182" t="s">
+        <v>790</v>
+      </c>
+      <c r="B182">
+        <v>11093</v>
+      </c>
+      <c r="C182" s="43" t="s">
+        <v>791</v>
+      </c>
+      <c r="D182" s="70">
+        <v>2</v>
+      </c>
+      <c r="E182" s="71">
+        <v>2</v>
+      </c>
+      <c r="F182" s="43" t="s">
+        <v>791</v>
+      </c>
+      <c r="G182" s="43" t="s">
+        <v>791</v>
+      </c>
+      <c r="H182" s="43" t="s">
+        <v>791</v>
+      </c>
+      <c r="I182" s="43" t="s">
+        <v>791</v>
+      </c>
+      <c r="J182" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="K182" s="68">
+        <v>0</v>
+      </c>
+      <c r="L182" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="M182" s="68">
+        <v>0</v>
+      </c>
+      <c r="N182" s="68">
+        <v>2</v>
+      </c>
+      <c r="O182" s="68">
+        <v>0</v>
+      </c>
+      <c r="P182" s="68"/>
+      <c r="Q182" s="68"/>
+      <c r="R182" s="68">
+        <v>2</v>
+      </c>
+      <c r="S182" s="41">
+        <v>0</v>
+      </c>
+      <c r="T182" s="72">
+        <v>1</v>
+      </c>
+      <c r="U182" s="72">
+        <v>0</v>
+      </c>
+      <c r="V182" s="72">
+        <v>0</v>
+      </c>
+      <c r="W182" s="68"/>
+      <c r="X182" s="68"/>
+      <c r="Y182" s="68"/>
+      <c r="Z182" s="68"/>
+      <c r="AA182" s="68"/>
+      <c r="AB182" s="68"/>
+      <c r="AC182" s="68"/>
+      <c r="AD182" s="68"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="S1:S180" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="S1:S181" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B92">
+    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F100">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G100">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H100">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I100">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B111">
+    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B134">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B135">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F165">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G165">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H165">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B166">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C166">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C167">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F168">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G168">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H168">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I168">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F169">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G169">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H169">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I169">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C180">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F180">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G180">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H180">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I180">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:B27">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67:B73">
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B93:B110">
+    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B112:B115">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B116:B119">
+    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B120:B133">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B136:B141">
     <cfRule type="duplicateValues" dxfId="0" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B77">
+  <conditionalFormatting sqref="B152:B156">
     <cfRule type="duplicateValues" dxfId="0" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+  <conditionalFormatting sqref="B162:B164">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F100">
+  <conditionalFormatting sqref="B167:B182">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C162:C164">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C168:C174">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C175:C179">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C181:C182">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F157:F161">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F170:F174">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F175:F179">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F181:F182">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G157:G161">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G170:G174">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G175:G179">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G181:G182">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H157:H161">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H170:H174">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H175:H179">
     <cfRule type="duplicateValues" dxfId="0" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G100">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  <conditionalFormatting sqref="H181:H182">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H100">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  <conditionalFormatting sqref="I157:I161">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I100">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="I170:I174">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  <conditionalFormatting sqref="I175:I179">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B134">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B135">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B166">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F168">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G168">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H168">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I168">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F169">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G169">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H169">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I169">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C180">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F180">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G180">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H180">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I180">
+  <conditionalFormatting sqref="I181:I182">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26:B27">
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  <conditionalFormatting sqref="B1:B25 B28:B43 B45 B47:B66 B74 B78:B91 B142:B151">
+    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B67:B73">
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B93:B110">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B112:B115">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B116:B119">
+  <conditionalFormatting sqref="C1:C161 C165 C183:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B120:B133">
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B136:B141">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B152:B156">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B162:B164">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B167:B180">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C162:C164">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C168:C174">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C175:C179">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F157:F161">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F170:F174">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F175:F179">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G157:G161">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G170:G174">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G175:G179">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H157:H161">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H170:H174">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H175:H179">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I157:I161">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I170:I174">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I175:I179">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B25 B28:B43 B45 B47:B66 B74 B78:B91 B142:B151">
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C161 C165 C181:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B46 B48 B50 B52 B54 B56 B58 B60">
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3">
@@ -18173,18 +18350,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B1" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:2">
       <c r="A2" s="32" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:2">
@@ -18200,7 +18377,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -18208,7 +18385,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -18216,7 +18393,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -18224,7 +18401,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -18232,7 +18409,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -18240,7 +18417,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -18248,7 +18425,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -18256,7 +18433,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -18264,7 +18441,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -18272,7 +18449,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -18280,7 +18457,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -18288,7 +18465,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -18296,7 +18473,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
   </sheetData>
@@ -18323,16 +18500,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D1" s="23" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:6">
@@ -18374,12 +18551,12 @@
         <v>121</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="30" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B5" s="30">
         <v>3002</v>
@@ -18402,7 +18579,7 @@
         <v>101</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -18416,12 +18593,12 @@
         <v>102</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="30" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="B8" s="30">
         <v>3005</v>
@@ -18430,12 +18607,12 @@
         <v>116</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="30" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B9" s="30">
         <v>3006</v>
@@ -18444,12 +18621,12 @@
         <v>201</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="30" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B10" s="30">
         <v>3007</v>
@@ -18458,12 +18635,12 @@
         <v>202</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="30" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="B11" s="30">
         <v>3008</v>
@@ -18472,12 +18649,12 @@
         <v>203</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="30" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B12" s="30">
         <v>3009</v>
@@ -18486,12 +18663,12 @@
         <v>301</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="30" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B13" s="30">
         <v>3010</v>
@@ -18500,12 +18677,12 @@
         <v>302</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="30" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="B14" s="30">
         <v>3011</v>
@@ -18514,7 +18691,7 @@
         <v>303</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -18547,7 +18724,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="30" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B17" s="30">
         <v>3014</v>
@@ -18556,12 +18733,12 @@
         <v>2002</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="30" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B18" s="30">
         <v>3015</v>
@@ -18575,7 +18752,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="30" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B19" s="30">
         <v>3016</v>
@@ -18584,26 +18761,26 @@
         <v>447</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="31" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B20" s="31">
         <v>3017</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="30" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B21" s="30">
         <v>3018</v>
@@ -18612,7 +18789,7 @@
         <v>115</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -18626,12 +18803,12 @@
         <v>424</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="30" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B23" s="30">
         <v>3020</v>
@@ -18640,12 +18817,12 @@
         <v>448</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="30" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B24" s="30">
         <v>3021</v>
@@ -18654,12 +18831,12 @@
         <v>437</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="30" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B25" s="30">
         <v>3022</v>
@@ -18668,12 +18845,12 @@
         <v>438</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="30" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B26" s="30">
         <v>3023</v>
@@ -18682,12 +18859,12 @@
         <v>439</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="30" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B27" s="30">
         <v>3024</v>
@@ -18696,292 +18873,292 @@
         <v>440</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="31" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B28" s="31">
         <v>3025</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="31" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B29" s="31">
         <v>3026</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="31" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B30" s="31">
         <v>3027</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="31" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B31" s="31">
         <v>3028</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="31" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B32" s="31">
         <v>3029</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="31" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B33" s="31">
         <v>3030</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="31" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B34" s="31">
         <v>3031</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="31" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="B35" s="31">
         <v>3032</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="31" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B36" s="31">
         <v>3033</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="31" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B37" s="31">
         <v>3034</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="31" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B38" s="31">
         <v>3035</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="31" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B39" s="31">
         <v>3036</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="31" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B40" s="31">
         <v>3037</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="31" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B41" s="31">
         <v>3038</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="31" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B42" s="31">
         <v>3039</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="31" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B43" s="31">
         <v>3040</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="31" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B44" s="31">
         <v>3041</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="31" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B45" s="31">
         <v>3042</v>
       </c>
       <c r="C45" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D45" s="31" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="31" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B46" s="31">
         <v>3043</v>
       </c>
       <c r="C46" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="31" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B47" s="31">
         <v>3044</v>
       </c>
       <c r="C47" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="30" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B48" s="30">
         <v>3045</v>
@@ -18990,12 +19167,12 @@
         <v>429</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="30" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B49" s="30">
         <v>3046</v>
@@ -19004,12 +19181,12 @@
         <v>430</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="30" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B50" s="30">
         <v>3047</v>
@@ -19018,12 +19195,12 @@
         <v>431</v>
       </c>
       <c r="D50" s="30" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="30" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B51" s="30">
         <v>3048</v>
@@ -19032,12 +19209,12 @@
         <v>432</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="30" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B52" s="30">
         <v>3049</v>
@@ -19046,12 +19223,12 @@
         <v>467</v>
       </c>
       <c r="D52" s="30" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="30" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B53" s="30">
         <v>3050</v>
@@ -19060,12 +19237,12 @@
         <v>468</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="30" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B54" s="30">
         <v>3051</v>
@@ -19074,12 +19251,12 @@
         <v>433</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="30" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B55" s="30">
         <v>3052</v>
@@ -19088,12 +19265,12 @@
         <v>434</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="30" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B56" s="30">
         <v>3053</v>
@@ -19102,12 +19279,12 @@
         <v>435</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="30" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B57" s="30">
         <v>3054</v>
@@ -19116,12 +19293,12 @@
         <v>436</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="30" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B58" s="30">
         <v>3055</v>
@@ -19130,12 +19307,12 @@
         <v>450</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="30" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B59" s="30">
         <v>3056</v>
@@ -19144,40 +19321,40 @@
         <v>451</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="31" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B60" s="31">
         <v>3057</v>
       </c>
       <c r="C60" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D60" s="31" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="31" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B61" s="31">
         <v>3058</v>
       </c>
       <c r="C61" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D61" s="31" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="30" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B62" s="30">
         <v>3059</v>
@@ -19186,12 +19363,12 @@
         <v>117</v>
       </c>
       <c r="D62" s="30" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="30" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B63" s="30">
         <v>3060</v>
@@ -19200,12 +19377,12 @@
         <v>118</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="30" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B64" s="30">
         <v>3061</v>
@@ -19214,12 +19391,12 @@
         <v>1007</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="30" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B65" s="30">
         <v>3062</v>
@@ -19228,12 +19405,12 @@
         <v>1008</v>
       </c>
       <c r="D65" s="30" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="30" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B66" s="30">
         <v>3063</v>
@@ -19242,12 +19419,12 @@
         <v>417</v>
       </c>
       <c r="D66" s="30" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="30" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B67" s="30">
         <v>3064</v>
@@ -19256,12 +19433,12 @@
         <v>418</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="30" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="B68" s="30">
         <v>3065</v>
@@ -19270,12 +19447,12 @@
         <v>419</v>
       </c>
       <c r="D68" s="30" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="30" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="B69" s="30">
         <v>3066</v>
@@ -19284,12 +19461,12 @@
         <v>427</v>
       </c>
       <c r="D69" s="30" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="30" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="B70" s="30">
         <v>3067</v>
@@ -19298,12 +19475,12 @@
         <v>428</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="30" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B71" s="30">
         <v>3068</v>
@@ -19312,12 +19489,12 @@
         <v>505</v>
       </c>
       <c r="D71" s="30" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="30" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B72" s="30">
         <v>3069</v>
@@ -19326,12 +19503,12 @@
         <v>511</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="30" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B73" s="30">
         <v>3070</v>
@@ -19340,12 +19517,12 @@
         <v>513</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="30" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B74" s="30">
         <v>3071</v>
@@ -19354,7 +19531,7 @@
         <v>514</v>
       </c>
       <c r="D74" s="30" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -19368,12 +19545,12 @@
         <v>515</v>
       </c>
       <c r="D75" s="30" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="30" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B76" s="30">
         <v>3073</v>
@@ -19382,12 +19559,12 @@
         <v>516</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="30" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B77" s="30">
         <v>3074</v>
@@ -19421,7 +19598,7 @@
         <v>3076</v>
       </c>
       <c r="C79" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D79" s="31" t="s">
         <v>321</v>
@@ -19435,7 +19612,7 @@
         <v>3077</v>
       </c>
       <c r="C80" s="31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D80" s="31" t="s">
         <v>325</v>
@@ -19452,7 +19629,7 @@
         <v>110</v>
       </c>
       <c r="D81" s="30" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -19466,7 +19643,7 @@
         <v>111</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
   </sheetData>
@@ -19498,27 +19675,27 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="6" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>36</v>
@@ -19527,7 +19704,7 @@
         <v>37</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>48</v>
@@ -19561,10 +19738,10 @@
         <v>10031</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -19573,7 +19750,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -19581,10 +19758,10 @@
         <v>10032</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -19593,7 +19770,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -19601,19 +19778,19 @@
         <v>10033</v>
       </c>
       <c r="B6" s="21" t="s">
+        <v>953</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>950</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -19621,10 +19798,10 @@
         <v>10034</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
@@ -19633,7 +19810,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -19641,10 +19818,10 @@
         <v>10035</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -19653,7 +19830,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -19661,10 +19838,10 @@
         <v>10036</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -19673,7 +19850,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -19681,10 +19858,10 @@
         <v>10037</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -19693,7 +19870,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -19701,10 +19878,10 @@
         <v>10038</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
@@ -19713,7 +19890,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -19721,10 +19898,10 @@
         <v>10039</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D12" s="2">
         <v>2</v>
@@ -19733,7 +19910,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -19741,10 +19918,10 @@
         <v>10040</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
@@ -19753,7 +19930,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -19761,10 +19938,10 @@
         <v>10041</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
@@ -19773,7 +19950,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -19781,10 +19958,10 @@
         <v>10042</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
@@ -19793,7 +19970,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -19801,10 +19978,10 @@
         <v>10043</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -19813,7 +19990,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -19821,10 +19998,10 @@
         <v>10044</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -19833,7 +20010,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -19841,10 +20018,10 @@
         <v>10045</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
@@ -19853,7 +20030,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -19861,10 +20038,10 @@
         <v>10046</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
@@ -19873,7 +20050,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -19881,10 +20058,10 @@
         <v>10047</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -19893,7 +20070,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -19901,10 +20078,10 @@
         <v>10048</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
@@ -19913,7 +20090,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -19921,10 +20098,10 @@
         <v>10049</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -19933,7 +20110,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -19941,10 +20118,10 @@
         <v>10050</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="D23" s="2">
         <v>2</v>
@@ -19953,7 +20130,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -19961,10 +20138,10 @@
         <v>10051</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -19973,7 +20150,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -19981,10 +20158,10 @@
         <v>10052</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
@@ -19993,7 +20170,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -20004,7 +20181,7 @@
         <v>618</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
@@ -20013,7 +20190,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -20024,7 +20201,7 @@
         <v>518</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -20033,7 +20210,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -20041,10 +20218,10 @@
         <v>10055</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
@@ -20053,7 +20230,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -20061,10 +20238,10 @@
         <v>10056</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
@@ -20073,7 +20250,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -20081,10 +20258,10 @@
         <v>10057</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="D30" s="2">
         <v>2</v>
@@ -20093,7 +20270,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -20101,10 +20278,10 @@
         <v>10058</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D31" s="2">
         <v>2</v>
@@ -20113,7 +20290,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -20121,10 +20298,10 @@
         <v>10059</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D32" s="2">
         <v>2</v>
@@ -20133,7 +20310,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -20141,10 +20318,10 @@
         <v>10060</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="D33" s="2">
         <v>2</v>
@@ -20153,7 +20330,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -20161,10 +20338,10 @@
         <v>10061</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D34" s="2">
         <v>2</v>
@@ -20173,7 +20350,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -20181,10 +20358,10 @@
         <v>10062</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D35" s="2">
         <v>2</v>
@@ -20193,7 +20370,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -20201,10 +20378,10 @@
         <v>10063</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D36" s="2">
         <v>2</v>
@@ -20213,7 +20390,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -20221,10 +20398,10 @@
         <v>10064</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D37" s="2">
         <v>2</v>
@@ -20233,7 +20410,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -20241,10 +20418,10 @@
         <v>10065</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D38" s="2">
         <v>2</v>
@@ -20253,7 +20430,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -20264,7 +20441,7 @@
         <v>217</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D39" s="2">
         <v>2</v>
@@ -20273,7 +20450,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -20284,7 +20461,7 @@
         <v>222</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D40" s="2">
         <v>2</v>
@@ -20293,7 +20470,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -20301,10 +20478,10 @@
         <v>10068</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="D41" s="2">
         <v>2</v>
@@ -20313,7 +20490,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -20321,10 +20498,10 @@
         <v>10069</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="D42" s="2">
         <v>2</v>
@@ -20333,7 +20510,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -20341,10 +20518,10 @@
         <v>10070</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="D43" s="2">
         <v>2</v>
@@ -20353,7 +20530,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -20361,10 +20538,10 @@
         <v>10071</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D44" s="2">
         <v>2</v>
@@ -20373,7 +20550,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -20381,10 +20558,10 @@
         <v>10072</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D45" s="2">
         <v>2</v>
@@ -20393,7 +20570,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -20401,10 +20578,10 @@
         <v>10073</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D46" s="2">
         <v>2</v>
@@ -20413,7 +20590,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -20421,10 +20598,10 @@
         <v>10074</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="D47" s="2">
         <v>2</v>
@@ -20433,7 +20610,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -20441,10 +20618,10 @@
         <v>10075</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="D48" s="2">
         <v>2</v>
@@ -20453,7 +20630,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -20461,10 +20638,10 @@
         <v>10076</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="D49" s="2">
         <v>2</v>
@@ -20473,7 +20650,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -20481,10 +20658,10 @@
         <v>10077</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
@@ -20493,7 +20670,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -20501,10 +20678,10 @@
         <v>10078</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D51" s="2">
         <v>2</v>
@@ -20513,7 +20690,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -20521,10 +20698,10 @@
         <v>10079</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D52" s="2">
         <v>2</v>
@@ -20533,7 +20710,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -20541,10 +20718,10 @@
         <v>10080</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="D53" s="2">
         <v>2</v>
@@ -20553,7 +20730,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -20561,10 +20738,10 @@
         <v>10081</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D54" s="2">
         <v>2</v>
@@ -20573,7 +20750,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -20581,10 +20758,10 @@
         <v>10082</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="D55" s="2">
         <v>2</v>
@@ -20593,7 +20770,7 @@
         <v>2</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -20601,10 +20778,10 @@
         <v>10083</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D56" s="2">
         <v>2</v>
@@ -20613,7 +20790,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -20621,10 +20798,10 @@
         <v>10084</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D57" s="2">
         <v>2</v>
@@ -20633,7 +20810,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="58" ht="34.5" spans="1:6">
@@ -20641,10 +20818,10 @@
         <v>10085</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D58" s="2">
         <v>2</v>
@@ -20653,7 +20830,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="59" ht="34.5" spans="1:6">
@@ -20661,10 +20838,10 @@
         <v>10086</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="D59" s="2">
         <v>2</v>
@@ -20673,7 +20850,7 @@
         <v>2</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -20681,10 +20858,10 @@
         <v>10087</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="D60" s="2">
         <v>2</v>
@@ -20693,7 +20870,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -20701,10 +20878,10 @@
         <v>10088</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="D61" s="2">
         <v>2</v>
@@ -20713,7 +20890,7 @@
         <v>2</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -20721,10 +20898,10 @@
         <v>10089</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D62" s="2">
         <v>2</v>
@@ -20733,7 +20910,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -20741,10 +20918,10 @@
         <v>10090</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="D63" s="2">
         <v>2</v>
@@ -20753,7 +20930,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -20761,10 +20938,10 @@
         <v>10091</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D64" s="2">
         <v>2</v>
@@ -20773,7 +20950,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -20781,10 +20958,10 @@
         <v>10092</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D65" s="2">
         <v>2</v>
@@ -20793,7 +20970,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -20801,10 +20978,10 @@
         <v>10093</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D66" s="2">
         <v>2</v>
@@ -20813,7 +20990,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -20821,10 +20998,10 @@
         <v>10094</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="D67" s="2">
         <v>2</v>
@@ -20833,7 +21010,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -20841,10 +21018,10 @@
         <v>10095</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D68" s="2">
         <v>2</v>
@@ -20853,7 +21030,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -20861,10 +21038,10 @@
         <v>10096</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D69" s="2">
         <v>2</v>
@@ -20873,7 +21050,7 @@
         <v>2</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -20881,10 +21058,10 @@
         <v>10097</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D70" s="2">
         <v>2</v>
@@ -20893,7 +21070,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -20901,10 +21078,10 @@
         <v>10098</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="D71" s="2">
         <v>2</v>
@@ -20913,7 +21090,7 @@
         <v>2</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -20921,10 +21098,10 @@
         <v>10099</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D72" s="2">
         <v>2</v>
@@ -20933,7 +21110,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -20941,10 +21118,10 @@
         <v>10100</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
@@ -20953,7 +21130,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -20961,10 +21138,10 @@
         <v>10101</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="D74" s="2">
         <v>2</v>
@@ -20973,7 +21150,7 @@
         <v>2</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -20981,10 +21158,10 @@
         <v>10102</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D75" s="2">
         <v>2</v>
@@ -20993,7 +21170,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -21001,10 +21178,10 @@
         <v>10103</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D76" s="2">
         <v>2</v>
@@ -21013,7 +21190,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -21021,10 +21198,10 @@
         <v>10104</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="D77" s="2">
         <v>2</v>
@@ -21033,7 +21210,7 @@
         <v>2</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -21041,10 +21218,10 @@
         <v>10105</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="D78" s="2">
         <v>2</v>
@@ -21053,7 +21230,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -21061,10 +21238,10 @@
         <v>10106</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D79" s="2">
         <v>2</v>
@@ -21073,7 +21250,7 @@
         <v>2</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -21081,10 +21258,10 @@
         <v>10107</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D80" s="2">
         <v>2</v>
@@ -21093,7 +21270,7 @@
         <v>2</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -21101,10 +21278,10 @@
         <v>10108</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D81" s="2">
         <v>2</v>
@@ -21113,7 +21290,7 @@
         <v>2</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -21121,10 +21298,10 @@
         <v>10109</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="D82" s="2">
         <v>2</v>
@@ -21133,7 +21310,7 @@
         <v>2</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -21141,10 +21318,10 @@
         <v>10110</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="D83" s="2">
         <v>2</v>
@@ -21153,7 +21330,7 @@
         <v>2</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -21161,10 +21338,10 @@
         <v>10111</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D84" s="2">
         <v>2</v>
@@ -21173,7 +21350,7 @@
         <v>2</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -21181,10 +21358,10 @@
         <v>10112</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="D85" s="2">
         <v>2</v>
@@ -21193,7 +21370,7 @@
         <v>2</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -21201,10 +21378,10 @@
         <v>10113</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="D86" s="2">
         <v>2</v>
@@ -21213,7 +21390,7 @@
         <v>2</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -21221,10 +21398,10 @@
         <v>10114</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D87" s="2">
         <v>2</v>
@@ -21233,7 +21410,7 @@
         <v>2</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -21241,10 +21418,10 @@
         <v>10116</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="D88" s="2">
         <v>2</v>
@@ -21253,7 +21430,7 @@
         <v>2</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -21261,10 +21438,10 @@
         <v>10117</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="D89" s="2">
         <v>0</v>
@@ -21273,7 +21450,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -21281,10 +21458,10 @@
         <v>10118</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D90" s="2">
         <v>2</v>
@@ -21293,7 +21470,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -21301,10 +21478,10 @@
         <v>10119</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="D91" s="2">
         <v>2</v>
@@ -21313,7 +21490,7 @@
         <v>2</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -21333,7 +21510,7 @@
         <v>2</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -21341,7 +21518,7 @@
         <v>10121</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D93" s="2">
         <v>2</v>
@@ -21350,7 +21527,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -21358,10 +21535,10 @@
         <v>10122</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="D94" s="2">
         <v>0</v>
@@ -21370,7 +21547,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -21378,10 +21555,10 @@
         <v>10123</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D95" s="2">
         <v>2</v>
@@ -21390,7 +21567,7 @@
         <v>2</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -21398,10 +21575,10 @@
         <v>10124</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="D96" s="2">
         <v>2</v>
@@ -21410,7 +21587,7 @@
         <v>2</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -21418,10 +21595,10 @@
         <v>10125</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="D97" s="2">
         <v>2</v>
@@ -21430,7 +21607,7 @@
         <v>2</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -21438,10 +21615,10 @@
         <v>10126</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D98" s="2">
         <v>2</v>
@@ -21450,7 +21627,7 @@
         <v>2</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -21458,10 +21635,10 @@
         <v>10127</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D99" s="2">
         <v>2</v>
@@ -21470,7 +21647,7 @@
         <v>2</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -21478,10 +21655,10 @@
         <v>10128</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="D100" s="2">
         <v>2</v>
@@ -21490,7 +21667,7 @@
         <v>2</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -21498,10 +21675,10 @@
         <v>10129</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="D101" s="2">
         <v>0</v>
@@ -21510,7 +21687,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -21518,10 +21695,10 @@
         <v>10130</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="D102" s="2">
         <v>2</v>
@@ -21530,7 +21707,7 @@
         <v>2</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -21538,10 +21715,10 @@
         <v>10131</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="D103" s="2">
         <v>0</v>
@@ -21550,7 +21727,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -21558,10 +21735,10 @@
         <v>10132</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="D104" s="2">
         <v>2</v>
@@ -21570,7 +21747,7 @@
         <v>2</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -21578,10 +21755,10 @@
         <v>10134</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="D105" s="2">
         <v>2</v>
@@ -21590,7 +21767,7 @@
         <v>2</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -21598,10 +21775,10 @@
         <v>10135</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="D106" s="2">
         <v>2</v>
@@ -21610,7 +21787,7 @@
         <v>2</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -21618,10 +21795,10 @@
         <v>10136</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="D107" s="2">
         <v>2</v>
@@ -21630,7 +21807,7 @@
         <v>2</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -21638,10 +21815,10 @@
         <v>10137</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="D108" s="2">
         <v>2</v>
@@ -21650,7 +21827,7 @@
         <v>2</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -21658,10 +21835,10 @@
         <v>10138</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="D109" s="2">
         <v>2</v>
@@ -21670,7 +21847,7 @@
         <v>2</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -21678,10 +21855,10 @@
         <v>10139</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D110" s="2">
         <v>0</v>
@@ -21690,7 +21867,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -21698,10 +21875,10 @@
         <v>10140</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="D111" s="2">
         <v>2</v>
@@ -21710,7 +21887,7 @@
         <v>2</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -21718,10 +21895,10 @@
         <v>10141</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="D112" s="2">
         <v>0</v>
@@ -21730,7 +21907,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -21738,10 +21915,10 @@
         <v>10142</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="D113" s="2">
         <v>2</v>
@@ -21750,7 +21927,7 @@
         <v>2</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -21758,10 +21935,10 @@
         <v>10143</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="D114" s="2">
         <v>2</v>
@@ -21770,7 +21947,7 @@
         <v>2</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -21778,10 +21955,10 @@
         <v>10144</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="D115" s="2">
         <v>2</v>
@@ -21790,7 +21967,7 @@
         <v>2</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -21798,10 +21975,10 @@
         <v>10145</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="D116" s="2">
         <v>0</v>
@@ -21810,7 +21987,7 @@
         <v>0</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -21818,10 +21995,10 @@
         <v>10146</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="D117" s="2">
         <v>2</v>
@@ -21830,7 +22007,7 @@
         <v>2</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -21838,10 +22015,10 @@
         <v>10147</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="D118" s="2">
         <v>2</v>
@@ -21850,7 +22027,7 @@
         <v>2</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -21858,10 +22035,10 @@
         <v>10148</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="D119" s="2">
         <v>0</v>
@@ -21870,7 +22047,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -21878,10 +22055,10 @@
         <v>10149</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="D120" s="2">
         <v>0</v>
@@ -21890,7 +22067,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -21898,10 +22075,10 @@
         <v>10150</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="D121" s="2">
         <v>0</v>
@@ -21910,7 +22087,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -21918,10 +22095,10 @@
         <v>10151</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="D122" s="2">
         <v>0</v>
@@ -21930,7 +22107,7 @@
         <v>0</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -21938,10 +22115,10 @@
         <v>10152</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="D123" s="2">
         <v>0</v>
@@ -21950,7 +22127,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -21958,10 +22135,10 @@
         <v>10153</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="D124" s="2">
         <v>0</v>
@@ -21970,7 +22147,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -21978,10 +22155,10 @@
         <v>10154</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="D125" s="2">
         <v>0</v>
@@ -21990,7 +22167,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -21998,10 +22175,10 @@
         <v>10155</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="D126" s="2">
         <v>0</v>
@@ -22010,7 +22187,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -22018,10 +22195,10 @@
         <v>10156</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="D127" s="2">
         <v>0</v>
@@ -22030,7 +22207,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -22038,10 +22215,10 @@
         <v>10157</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="D128" s="2">
         <v>0</v>
@@ -22050,7 +22227,7 @@
         <v>0</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -22058,10 +22235,10 @@
         <v>10158</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="D129" s="2">
         <v>0</v>
@@ -22070,7 +22247,7 @@
         <v>0</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -22078,10 +22255,10 @@
         <v>10159</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="D130" s="2">
         <v>0</v>
@@ -22090,7 +22267,7 @@
         <v>0</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -22098,10 +22275,10 @@
         <v>10160</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="D131" s="2">
         <v>0</v>
@@ -22110,7 +22287,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -22118,10 +22295,10 @@
         <v>10161</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="D132" s="2">
         <v>0</v>
@@ -22130,7 +22307,7 @@
         <v>0</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:6">
@@ -22138,10 +22315,10 @@
         <v>10162</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="D133" s="2">
         <v>0</v>
@@ -22150,7 +22327,7 @@
         <v>0</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:6">
@@ -22158,10 +22335,10 @@
         <v>10167</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="D134" s="2">
         <v>2</v>
@@ -22170,7 +22347,7 @@
         <v>2</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -22178,10 +22355,10 @@
         <v>10168</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="D135" s="2">
         <v>2</v>
@@ -22190,7 +22367,7 @@
         <v>2</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -22198,10 +22375,10 @@
         <v>10169</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="D136" s="2">
         <v>2</v>
@@ -22210,7 +22387,7 @@
         <v>2</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -22218,10 +22395,10 @@
         <v>10170</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="D137" s="2">
         <v>2</v>
@@ -22230,7 +22407,7 @@
         <v>2</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -22238,10 +22415,10 @@
         <v>10171</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="D138" s="2">
         <v>2</v>
@@ -22250,7 +22427,7 @@
         <v>2</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -22258,10 +22435,10 @@
         <v>10172</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="D139" s="2">
         <v>2</v>
@@ -22270,7 +22447,7 @@
         <v>2</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -22278,10 +22455,10 @@
         <v>10173</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="D140" s="2">
         <v>2</v>
@@ -22290,7 +22467,7 @@
         <v>2</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -22298,10 +22475,10 @@
         <v>10174</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="D141" s="2">
         <v>2</v>
@@ -22310,7 +22487,7 @@
         <v>2</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -22318,10 +22495,10 @@
         <v>10175</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="D142" s="2">
         <v>2</v>
@@ -22330,7 +22507,7 @@
         <v>2</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -22338,10 +22515,10 @@
         <v>10176</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="D143" s="2">
         <v>2</v>
@@ -22350,7 +22527,7 @@
         <v>2</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -22358,10 +22535,10 @@
         <v>10177</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="D144" s="2">
         <v>2</v>
@@ -22370,7 +22547,7 @@
         <v>2</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" spans="1:6">
@@ -22378,10 +22555,10 @@
         <v>10178</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="D145" s="2">
         <v>2</v>
@@ -22390,7 +22567,7 @@
         <v>2</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="146" s="1" customFormat="1" spans="1:6">
@@ -22398,10 +22575,10 @@
         <v>10179</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="D146" s="2">
         <v>2</v>
@@ -22410,7 +22587,7 @@
         <v>2</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="147" s="1" customFormat="1" spans="1:6">
@@ -22418,10 +22595,10 @@
         <v>10180</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="D147" s="2">
         <v>2</v>
@@ -22430,7 +22607,7 @@
         <v>2</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -22438,10 +22615,10 @@
         <v>10181</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="D148" s="2">
         <v>2</v>
@@ -22455,10 +22632,10 @@
         <v>10182</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="D149" s="2">
         <v>2</v>
@@ -22472,10 +22649,10 @@
         <v>10183</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="D150" s="2">
         <v>2</v>
@@ -22489,10 +22666,10 @@
         <v>10184</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="D151" s="2">
         <v>2</v>
@@ -22506,10 +22683,10 @@
         <v>10185</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D152" s="2">
         <v>2</v>
@@ -22523,10 +22700,10 @@
         <v>10186</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="D153" s="2">
         <v>2</v>
@@ -22540,10 +22717,10 @@
         <v>10187</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="D154" s="2">
         <v>2</v>
@@ -22557,10 +22734,10 @@
         <v>10188</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="D155" s="2">
         <v>2</v>
@@ -22574,10 +22751,10 @@
         <v>10189</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="D156" s="2">
         <v>2</v>
@@ -22591,10 +22768,10 @@
         <v>10190</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="D157" s="2">
         <v>2</v>
@@ -22608,10 +22785,10 @@
         <v>10191</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="D158" s="2">
         <v>2</v>
@@ -22625,10 +22802,10 @@
         <v>10192</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="D159" s="2">
         <v>2</v>
@@ -22642,10 +22819,10 @@
         <v>10193</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="D160" s="2">
         <v>2</v>
@@ -22659,10 +22836,10 @@
         <v>10194</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="D161" s="2">
         <v>2</v>
@@ -22676,10 +22853,10 @@
         <v>10195</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="D162" s="2">
         <v>2</v>
@@ -22693,10 +22870,10 @@
         <v>10196</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="D163" s="2">
         <v>2</v>
@@ -22710,10 +22887,10 @@
         <v>10197</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="D164" s="2">
         <v>2</v>
@@ -22727,10 +22904,10 @@
         <v>10198</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="D165" s="2">
         <v>2</v>
@@ -22744,10 +22921,10 @@
         <v>10199</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="D166" s="2">
         <v>2</v>
@@ -22761,10 +22938,10 @@
         <v>10200</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="D167" s="2">
         <v>2</v>
@@ -22778,10 +22955,10 @@
         <v>10201</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="D168" s="2">
         <v>2</v>
@@ -22795,10 +22972,10 @@
         <v>10202</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="D169" s="2">
         <v>2</v>
@@ -22812,10 +22989,10 @@
         <v>10203</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="D170" s="2">
         <v>2</v>
@@ -22829,10 +23006,10 @@
         <v>10204</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="D171" s="2">
         <v>2</v>
@@ -22846,10 +23023,10 @@
         <v>10205</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D172" s="2">
         <v>2</v>
@@ -22863,10 +23040,10 @@
         <v>10206</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="D173" s="2">
         <v>0</v>
@@ -22880,10 +23057,10 @@
         <v>10207</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="D174" s="2">
         <v>2</v>
@@ -22897,10 +23074,10 @@
         <v>10208</v>
       </c>
       <c r="B175" s="17" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="D175" s="2">
         <v>2</v>
@@ -22914,10 +23091,10 @@
         <v>10209</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="D176" s="2">
         <v>2</v>
@@ -22931,10 +23108,10 @@
         <v>10210</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="D177" s="2">
         <v>2</v>
@@ -22948,10 +23125,10 @@
         <v>10211</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="D178" s="2">
         <v>2</v>
@@ -22965,10 +23142,10 @@
         <v>10212</v>
       </c>
       <c r="B179" s="17" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="D179" s="2">
         <v>2</v>
@@ -22982,10 +23159,10 @@
         <v>10213</v>
       </c>
       <c r="B180" s="17" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="D180" s="2">
         <v>2</v>
@@ -22999,10 +23176,10 @@
         <v>10214</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="D181" s="2">
         <v>2</v>
@@ -23016,10 +23193,10 @@
         <v>10215</v>
       </c>
       <c r="B182" s="17" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="D182" s="2">
         <v>2</v>
@@ -23033,10 +23210,10 @@
         <v>10216</v>
       </c>
       <c r="B183" s="17" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="D183" s="2">
         <v>2</v>
@@ -23050,10 +23227,10 @@
         <v>10217</v>
       </c>
       <c r="B184" s="17" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="D184" s="2">
         <v>2</v>
@@ -23067,10 +23244,10 @@
         <v>10218</v>
       </c>
       <c r="B185" s="17" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="D185" s="2">
         <v>2</v>
@@ -23084,10 +23261,10 @@
         <v>10219</v>
       </c>
       <c r="B186" s="17" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="D186" s="2">
         <v>2</v>
@@ -23101,10 +23278,10 @@
         <v>10220</v>
       </c>
       <c r="B187" s="17" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="D187" s="2">
         <v>2</v>
@@ -23118,10 +23295,10 @@
         <v>10221</v>
       </c>
       <c r="B188" s="17" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="D188" s="2">
         <v>2</v>
@@ -23135,10 +23312,10 @@
         <v>10222</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="D189" s="2">
         <v>2</v>
@@ -23152,10 +23329,10 @@
         <v>10223</v>
       </c>
       <c r="B190" s="17" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="D190" s="2">
         <v>2</v>
@@ -23169,10 +23346,10 @@
         <v>10224</v>
       </c>
       <c r="B191" s="17" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="D191" s="2">
         <v>2</v>
@@ -23186,10 +23363,10 @@
         <v>10225</v>
       </c>
       <c r="B192" s="17" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="D192" s="2">
         <v>2</v>
@@ -23203,10 +23380,10 @@
         <v>10226</v>
       </c>
       <c r="B193" s="17" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="D193" s="2">
         <v>2</v>
@@ -23220,10 +23397,10 @@
         <v>10227</v>
       </c>
       <c r="B194" s="17" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="D194" s="2">
         <v>2</v>
@@ -23237,10 +23414,10 @@
         <v>10228</v>
       </c>
       <c r="B195" s="17" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="D195" s="2">
         <v>2</v>
@@ -23254,10 +23431,10 @@
         <v>10229</v>
       </c>
       <c r="B196" s="17" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="D196" s="2">
         <v>2</v>
@@ -23271,10 +23448,10 @@
         <v>10230</v>
       </c>
       <c r="B197" s="17" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="D197" s="2">
         <v>2</v>
@@ -23288,10 +23465,10 @@
         <v>10231</v>
       </c>
       <c r="B198" s="17" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="D198" s="2">
         <v>2</v>
@@ -23305,10 +23482,10 @@
         <v>10232</v>
       </c>
       <c r="B199" s="17" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="D199" s="2">
         <v>2</v>
@@ -23322,10 +23499,10 @@
         <v>10233</v>
       </c>
       <c r="B200" s="17" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="D200" s="2">
         <v>2</v>
@@ -23339,10 +23516,10 @@
         <v>10234</v>
       </c>
       <c r="B201" s="17" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="D201" s="2">
         <v>2</v>
@@ -23356,10 +23533,10 @@
         <v>10235</v>
       </c>
       <c r="B202" s="17" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="D202" s="2">
         <v>2</v>
@@ -23373,10 +23550,10 @@
         <v>10236</v>
       </c>
       <c r="B203" s="17" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="D203" s="2">
         <v>2</v>
@@ -23390,10 +23567,10 @@
         <v>10237</v>
       </c>
       <c r="B204" s="17" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="D204" s="2">
         <v>2</v>
@@ -23407,10 +23584,10 @@
         <v>10238</v>
       </c>
       <c r="B205" s="17" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="D205" s="2">
         <v>2</v>
@@ -23424,10 +23601,10 @@
         <v>10239</v>
       </c>
       <c r="B206" s="17" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="D206" s="2">
         <v>2</v>
@@ -23441,10 +23618,10 @@
         <v>10240</v>
       </c>
       <c r="B207" s="17" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="D207" s="2">
         <v>0</v>
@@ -23458,10 +23635,10 @@
         <v>10241</v>
       </c>
       <c r="B208" s="17" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="D208" s="2">
         <v>0</v>
@@ -23475,10 +23652,10 @@
         <v>10242</v>
       </c>
       <c r="B209" s="17" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="D209" s="2">
         <v>0</v>
@@ -23492,10 +23669,10 @@
         <v>10243</v>
       </c>
       <c r="B210" s="17" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="D210" s="2">
         <v>2</v>
@@ -23509,10 +23686,10 @@
         <v>10244</v>
       </c>
       <c r="B211" s="17" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="D211" s="2">
         <v>0</v>
@@ -23526,10 +23703,10 @@
         <v>10245</v>
       </c>
       <c r="B212" s="17" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="D212" s="2">
         <v>0</v>
@@ -23543,10 +23720,10 @@
         <v>10246</v>
       </c>
       <c r="B213" s="17" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="D213" s="2">
         <v>0</v>
@@ -23560,10 +23737,10 @@
         <v>10247</v>
       </c>
       <c r="B214" s="17" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="D214" s="2">
         <v>2</v>
@@ -23577,10 +23754,10 @@
         <v>10248</v>
       </c>
       <c r="B215" s="17" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="D215" s="2">
         <v>2</v>
@@ -23594,10 +23771,10 @@
         <v>10249</v>
       </c>
       <c r="B216" s="17" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="D216" s="2">
         <v>0</v>
@@ -23611,10 +23788,10 @@
         <v>10250</v>
       </c>
       <c r="B217" s="17" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="D217" s="2">
         <v>2</v>
@@ -23628,10 +23805,10 @@
         <v>10251</v>
       </c>
       <c r="B218" s="17" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="D218" s="2">
         <v>2</v>
@@ -23645,10 +23822,10 @@
         <v>10252</v>
       </c>
       <c r="B219" s="17" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="D219" s="2">
         <v>2</v>
@@ -23662,10 +23839,10 @@
         <v>10253</v>
       </c>
       <c r="B220" s="17" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="D220" s="2">
         <v>2</v>
@@ -23679,10 +23856,10 @@
         <v>10254</v>
       </c>
       <c r="B221" s="17" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="D221" s="2">
         <v>2</v>
@@ -23696,10 +23873,10 @@
         <v>10255</v>
       </c>
       <c r="B222" s="17" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="D222" s="2">
         <v>3</v>
@@ -23713,10 +23890,10 @@
         <v>10256</v>
       </c>
       <c r="B223" s="17" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="D223" s="2">
         <v>3</v>
@@ -23730,10 +23907,10 @@
         <v>10257</v>
       </c>
       <c r="B224" s="17" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="D224" s="2">
         <v>3</v>
@@ -23747,10 +23924,10 @@
         <v>10258</v>
       </c>
       <c r="B225" s="17" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="D225" s="2">
         <v>3</v>
@@ -23764,10 +23941,10 @@
         <v>10259</v>
       </c>
       <c r="B226" s="17" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="D226" s="2">
         <v>3</v>
@@ -23781,10 +23958,10 @@
         <v>10260</v>
       </c>
       <c r="B227" s="17" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="D227" s="2">
         <v>2</v>
@@ -23798,10 +23975,10 @@
         <v>10261</v>
       </c>
       <c r="B228" s="17" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="D228" s="2">
         <v>2</v>
@@ -23815,10 +23992,10 @@
         <v>10262</v>
       </c>
       <c r="B229" s="17" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="D229" s="2">
         <v>2</v>
@@ -23832,10 +24009,10 @@
         <v>10263</v>
       </c>
       <c r="B230" s="17" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="D230" s="2">
         <v>2</v>
@@ -23849,10 +24026,10 @@
         <v>10264</v>
       </c>
       <c r="B231" s="17" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="D231" s="2">
         <v>2</v>
@@ -23866,10 +24043,10 @@
         <v>10265</v>
       </c>
       <c r="B232" s="17" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="C232" s="21" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="D232" s="2">
         <v>2</v>
@@ -23883,10 +24060,10 @@
         <v>10266</v>
       </c>
       <c r="B233" s="17" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="C233" s="21" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="D233" s="2">
         <v>2</v>
@@ -23900,10 +24077,10 @@
         <v>10267</v>
       </c>
       <c r="B234" s="17" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="C234" s="21" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="D234" s="2">
         <v>2</v>
@@ -23917,10 +24094,10 @@
         <v>10268</v>
       </c>
       <c r="B235" s="17" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C235" s="21" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -23934,10 +24111,10 @@
         <v>10269</v>
       </c>
       <c r="B236" s="17" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="C236" s="21" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="D236" s="2">
         <v>2</v>
@@ -23951,10 +24128,10 @@
         <v>10270</v>
       </c>
       <c r="B237" s="17" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="C237" s="21" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="D237" s="2">
         <v>2</v>
@@ -23968,10 +24145,10 @@
         <v>10271</v>
       </c>
       <c r="B238" s="17" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="C238" s="21" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="D238" s="2">
         <v>2</v>
@@ -23985,10 +24162,10 @@
         <v>10272</v>
       </c>
       <c r="B239" s="17" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="C239" s="21" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="D239" s="2">
         <v>0</v>
@@ -24002,10 +24179,10 @@
         <v>10273</v>
       </c>
       <c r="B240" s="17" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="C240" s="21" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="D240" s="2">
         <v>0</v>
@@ -24019,10 +24196,10 @@
         <v>10274</v>
       </c>
       <c r="B241" s="17" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="C241" s="21" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="D241" s="2">
         <v>0</v>
@@ -24036,10 +24213,10 @@
         <v>10275</v>
       </c>
       <c r="B242" s="17" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="C242" s="21" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -24053,10 +24230,10 @@
         <v>10276</v>
       </c>
       <c r="B243" s="17" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="C243" s="21" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -24070,10 +24247,10 @@
         <v>10277</v>
       </c>
       <c r="B244" s="17" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="C244" s="21" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -24087,10 +24264,10 @@
         <v>10278</v>
       </c>
       <c r="B245" s="17" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="C245" s="21" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="D245" s="2">
         <v>2</v>
@@ -24104,10 +24281,10 @@
         <v>10279</v>
       </c>
       <c r="B246" s="17" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="C246" s="21" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="D246" s="2">
         <v>2</v>
@@ -24121,10 +24298,10 @@
         <v>10280</v>
       </c>
       <c r="B247" s="17" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="D247" s="2">
         <v>2</v>
@@ -24167,24 +24344,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>36</v>
@@ -24193,7 +24370,7 @@
         <v>37</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>48</v>
@@ -24221,10 +24398,10 @@
         <v>2110000010</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="D4" s="4">
         <v>0</v>
@@ -24238,10 +24415,10 @@
         <v>2110000011</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="D5" s="4">
         <v>0</v>
@@ -24255,10 +24432,10 @@
         <v>2110000012</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="D6" s="4">
         <v>0</v>
@@ -24272,10 +24449,10 @@
         <v>2110000020</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -24289,10 +24466,10 @@
         <v>2110000021</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -24306,10 +24483,10 @@
         <v>2110000030</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="D9" s="4">
         <v>0</v>
@@ -24323,10 +24500,10 @@
         <v>2110000031</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="D10" s="4">
         <v>0</v>
@@ -24340,10 +24517,10 @@
         <v>2110000040</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
@@ -24357,10 +24534,10 @@
         <v>2114000020</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
@@ -24374,10 +24551,10 @@
         <v>2120000010</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -24391,10 +24568,10 @@
         <v>2120000011</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
@@ -24408,10 +24585,10 @@
         <v>2120000020</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="D15" s="4">
         <v>0</v>
@@ -24425,10 +24602,10 @@
         <v>2120000030</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="D16" s="4">
         <v>0</v>
@@ -24442,10 +24619,10 @@
         <v>2120000040</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="D17" s="4">
         <v>0</v>
@@ -24459,10 +24636,10 @@
         <v>2120000060</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -24476,10 +24653,10 @@
         <v>2120000080</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="D19" s="4">
         <v>0</v>
@@ -24493,10 +24670,10 @@
         <v>2140000030</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="D20" s="4">
         <v>0</v>
@@ -24510,10 +24687,10 @@
         <v>2140000040</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
@@ -24527,10 +24704,10 @@
         <v>2140000050</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
@@ -24544,10 +24721,10 @@
         <v>2140000060</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="D23" s="4">
         <v>0</v>
@@ -24561,10 +24738,10 @@
         <v>2140000070</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="D24" s="4">
         <v>0</v>
@@ -24578,10 +24755,10 @@
         <v>2140000080</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="D25" s="4">
         <v>0</v>
@@ -24595,10 +24772,10 @@
         <v>2140000110</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="D26" s="4">
         <v>0</v>
@@ -24612,10 +24789,10 @@
         <v>2140000140</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -24629,10 +24806,10 @@
         <v>2140000150</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="D28" s="4">
         <v>0</v>
@@ -24646,10 +24823,10 @@
         <v>2140000160</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="D29" s="4">
         <v>0</v>
@@ -24663,10 +24840,10 @@
         <v>2140000170</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="D30" s="4">
         <v>0</v>
@@ -24680,10 +24857,10 @@
         <v>2140000180</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="D31" s="4">
         <v>0</v>
@@ -24697,10 +24874,10 @@
         <v>2150000010</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="D32" s="4">
         <v>0</v>
@@ -24714,10 +24891,10 @@
         <v>2150000020</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -24731,10 +24908,10 @@
         <v>2150000060</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="D34" s="4">
         <v>0</v>
@@ -24748,10 +24925,10 @@
         <v>2150000070</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="D35" s="4">
         <v>0</v>
@@ -24765,10 +24942,10 @@
         <v>2150000080</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="D36" s="4">
         <v>0</v>
@@ -24782,10 +24959,10 @@
         <v>2150000090</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D37" s="4">
         <v>0</v>
@@ -24799,10 +24976,10 @@
         <v>2150000091</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
@@ -24816,10 +24993,10 @@
         <v>2150000100</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="D39" s="4">
         <v>0</v>
@@ -24833,10 +25010,10 @@
         <v>2150000110</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="D40" s="4">
         <v>0</v>
@@ -24850,10 +25027,10 @@
         <v>2150100060</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="D41" s="4">
         <v>0</v>
@@ -24867,10 +25044,10 @@
         <v>2150100070</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="D42" s="4">
         <v>0</v>
@@ -24884,10 +25061,10 @@
         <v>2150100080</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
@@ -24901,10 +25078,10 @@
         <v>2150100090</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D44" s="4">
         <v>0</v>
@@ -24918,10 +25095,10 @@
         <v>2150100091</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D45" s="4">
         <v>0</v>
@@ -24935,10 +25112,10 @@
         <v>2150200060</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="D46" s="4">
         <v>0</v>
@@ -24952,10 +25129,10 @@
         <v>2150200070</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="D47" s="4">
         <v>0</v>
@@ -24969,10 +25146,10 @@
         <v>2150200080</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
@@ -24986,10 +25163,10 @@
         <v>2150200090</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D49" s="4">
         <v>0</v>
@@ -25003,10 +25180,10 @@
         <v>2150200091</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D50" s="4">
         <v>0</v>
@@ -25020,10 +25197,10 @@
         <v>2150300060</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="D51" s="4">
         <v>0</v>
@@ -25037,10 +25214,10 @@
         <v>2150300070</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="D52" s="4">
         <v>0</v>
@@ -25054,10 +25231,10 @@
         <v>2150300090</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
@@ -25071,10 +25248,10 @@
         <v>2150300091</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D54" s="4">
         <v>0</v>
@@ -25088,10 +25265,10 @@
         <v>2150400060</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="D55" s="4">
         <v>0</v>
@@ -25105,10 +25282,10 @@
         <v>2150400090</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D56" s="4">
         <v>0</v>
@@ -25122,10 +25299,10 @@
         <v>2150400091</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D57" s="4">
         <v>0</v>
@@ -25139,10 +25316,10 @@
         <v>2340000010</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
@@ -25156,10 +25333,10 @@
         <v>2340000020</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="D59" s="4">
         <v>2</v>
@@ -25173,10 +25350,10 @@
         <v>2340000030</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="D60" s="4">
         <v>2</v>
@@ -25190,10 +25367,10 @@
         <v>2340000040</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
@@ -25207,10 +25384,10 @@
         <v>2340000050</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="D62" s="4">
         <v>0</v>
@@ -25224,10 +25401,10 @@
         <v>2340000080</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="D63" s="2">
         <v>0</v>
@@ -25241,10 +25418,10 @@
         <v>3140000020</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="D64" s="4">
         <v>0</v>
@@ -25258,10 +25435,10 @@
         <v>3140000030</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="D65" s="4">
         <v>0</v>
@@ -25275,10 +25452,10 @@
         <v>3140000040</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="D66" s="4">
         <v>0</v>
@@ -25292,10 +25469,10 @@
         <v>2140000100</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
@@ -25309,10 +25486,10 @@
         <v>2150000470</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="D68" s="4">
         <v>0</v>
@@ -25326,10 +25503,10 @@
         <v>2150000480</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="D69" s="4">
         <v>0</v>
@@ -25343,10 +25520,10 @@
         <v>2150000490</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="D70" s="4">
         <v>0</v>
@@ -25360,10 +25537,10 @@
         <v>2150000500</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="D71" s="4">
         <v>0</v>
@@ -25377,10 +25554,10 @@
         <v>2150000510</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="D72" s="4">
         <v>0</v>
